--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45771</v>
+        <v>45644</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44812</v>
+        <v>45251</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>45812</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44951</v>
+        <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,8 +2011,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2060,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>45827</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2084,8 +2089,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2138,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2152,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45234</v>
+        <v>46044</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2158,7 +2168,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45827</v>
+        <v>45903</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2230,13 +2240,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2279,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45000</v>
+        <v>45919</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2308,13 +2313,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44782</v>
+        <v>45095</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45903</v>
+        <v>45926</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2459,8 +2459,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45251</v>
+        <v>45000</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2532,8 +2537,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45919</v>
+        <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2606,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45926</v>
+        <v>45000</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2694,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2737,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2744,7 +2754,7 @@
         <v>44972</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2767,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2810,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2824,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45000</v>
+        <v>45958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2829,13 +2839,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2883,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2897,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44972</v>
+        <v>45960</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2913,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2956,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2970,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44972</v>
+        <v>45968</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2986,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3029,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3043,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45958</v>
+        <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3053,8 +3058,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3107,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3121,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45188</v>
+        <v>46132</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3137,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3180,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3194,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45960</v>
+        <v>46132</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3210,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3253,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3267,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45197</v>
+        <v>46132</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3272,13 +3282,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3326,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3340,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3351,7 +3356,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45973</v>
+        <v>45216</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3423,13 +3428,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45975</v>
+        <v>45980</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3501,8 +3501,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3545,7 +3550,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3559,10 +3564,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44790</v>
+        <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3575,7 +3580,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3618,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3632,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45980</v>
+        <v>45827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3649,11 +3654,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3696,7 +3701,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46132</v>
+        <v>44516</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3726,7 +3731,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3774,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3788,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46132</v>
+        <v>45446</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3798,8 +3803,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3842,7 +3852,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3856,10 +3866,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46132</v>
+        <v>45188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3872,7 +3882,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3915,7 +3925,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3925,14 +3935,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45095</v>
+        <v>45211</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3945,7 +3955,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3988,7 +3998,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4002,10 +4012,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44972</v>
+        <v>45272</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4018,7 +4028,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4061,7 +4071,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4075,10 +4085,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45716</v>
+        <v>45448</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4091,7 +4101,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4134,7 +4144,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4148,10 +4158,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46044</v>
+        <v>46153</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4163,8 +4173,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4207,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4221,10 +4236,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44967</v>
+        <v>45679</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4236,13 +4251,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4295,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,10 +4309,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45272</v>
+        <v>46161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4314,8 +4324,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4358,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4372,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45827</v>
+        <v>46162</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4389,11 +4404,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4451,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4450,10 +4465,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45471</v>
+        <v>46162</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4465,8 +4480,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4509,7 +4529,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4523,10 +4543,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44516</v>
+        <v>44812</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4539,7 +4559,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4582,7 +4602,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4596,10 +4616,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46153</v>
+        <v>45588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4611,13 +4631,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4660,7 +4675,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4674,10 +4689,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46161</v>
+        <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4689,13 +4704,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46162</v>
+        <v>46244</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4767,13 +4777,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45628</v>
+        <v>46204</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4851,7 +4856,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>9.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4894,7 +4899,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4908,10 +4913,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46162</v>
+        <v>46204</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4925,11 +4930,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4972,7 +4977,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4986,10 +4991,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45181</v>
+        <v>46132</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5002,7 +5007,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5050,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5064,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45588</v>
+        <v>46205</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5074,8 +5079,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5118,7 +5128,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5132,10 +5142,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45448</v>
+        <v>46205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5147,8 +5157,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5191,7 +5206,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5205,10 +5220,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45631</v>
+        <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5221,7 +5236,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5264,7 +5279,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5274,14 +5289,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45211</v>
+        <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5294,7 +5309,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5337,7 +5352,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5351,10 +5366,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46244</v>
+        <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5367,7 +5382,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5410,7 +5425,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5424,10 +5439,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44476</v>
+        <v>46259</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5439,8 +5454,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5483,7 +5503,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5497,10 +5517,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46204</v>
+        <v>46272</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5512,13 +5532,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5561,7 +5576,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5575,10 +5590,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46205</v>
+        <v>45282</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5591,7 +5606,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5634,7 +5649,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5648,10 +5663,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46205</v>
+        <v>45181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5664,7 +5679,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5707,7 +5722,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5721,10 +5736,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46204</v>
+        <v>44782</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5736,13 +5751,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5785,7 +5795,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5799,10 +5809,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46205</v>
+        <v>44727</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5814,13 +5824,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5863,7 +5868,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5877,10 +5882,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46205</v>
+        <v>44476</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5892,13 +5897,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>6.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44727</v>
+        <v>44972</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45282</v>
+        <v>45420</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6087,7 +6087,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6101,10 +6101,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46132</v>
+        <v>45188</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6174,10 +6174,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46259</v>
+        <v>44972</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6189,13 +6189,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6233,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6247,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45420</v>
+        <v>45471</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6263,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6306,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6320,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44636</v>
+        <v>45251</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6336,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6379,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6394,14 +6389,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45699</v>
+        <v>45387</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6415,11 +6410,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6472,14 +6467,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45387</v>
+        <v>45251</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6491,13 +6486,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6540,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6554,10 +6544,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45251</v>
+        <v>44951</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6570,7 +6560,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6613,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6627,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6643,7 +6633,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6686,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6700,10 +6690,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46272</v>
+        <v>44957</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6716,7 +6706,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6759,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6773,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45744</v>
+        <v>45234</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6789,7 +6779,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6832,7 +6822,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6846,10 +6836,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45188</v>
+        <v>44967</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6861,8 +6851,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6905,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6919,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45251</v>
+        <v>45744</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6935,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6978,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6992,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45679</v>
+        <v>45699</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7007,8 +7002,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7051,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45783</v>
+        <v>44636</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45644</v>
+        <v>45628</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,8 +7153,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45812</v>
+        <v>45783</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7226,13 +7231,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7509,7 +7509,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7679,10 +7679,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 18303-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44648</v>
+        <v>44685</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1563,8 +1563,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18303-2022</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44685</v>
+        <v>45181</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1634,11 +1639,6 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45644</v>
+        <v>44648</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45812</v>
+        <v>45448</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1933,13 +1933,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45197</v>
+        <v>44812</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,13 +2006,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2060,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45827</v>
+        <v>45446</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2095,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2138,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2152,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46044</v>
+        <v>44951</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2168,7 +2158,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45903</v>
+        <v>44957</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,7 +2231,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45919</v>
+        <v>45234</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2304,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2347,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2361,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45095</v>
+        <v>45631</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2377,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2420,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2434,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45926</v>
+        <v>45903</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2459,13 +2449,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2493,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2518,14 +2503,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45000</v>
+        <v>45211</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2537,13 +2522,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2566,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2580,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44790</v>
+        <v>45919</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2596,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2639,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2653,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45000</v>
+        <v>45926</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2694,7 +2674,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2737,7 +2717,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2751,10 +2731,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44972</v>
+        <v>46132</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2767,7 +2747,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2810,7 +2790,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2824,10 +2804,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45958</v>
+        <v>46132</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2840,7 +2820,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2883,7 +2863,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2897,10 +2877,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45960</v>
+        <v>46132</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2913,7 +2893,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2956,7 +2936,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2970,10 +2950,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45968</v>
+        <v>45000</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2985,8 +2965,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3029,7 +3014,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3043,10 +3028,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45973</v>
+        <v>45958</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3058,13 +3043,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3107,7 +3087,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3121,10 +3101,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46132</v>
+        <v>44782</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3137,7 +3117,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3180,7 +3160,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3194,10 +3174,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46132</v>
+        <v>45960</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3210,7 +3190,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3253,7 +3233,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3267,10 +3247,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46132</v>
+        <v>45251</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3283,7 +3263,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3326,7 +3306,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3340,10 +3320,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45975</v>
+        <v>45716</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3356,7 +3336,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3399,7 +3379,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3413,10 +3393,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45216</v>
+        <v>45968</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3429,7 +3409,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3472,7 +3452,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3486,10 +3466,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45980</v>
+        <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3501,13 +3481,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3550,7 +3525,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3564,10 +3539,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45716</v>
+        <v>45827</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3579,8 +3554,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3623,7 +3603,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3637,10 +3617,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45827</v>
+        <v>45973</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3658,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3701,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3715,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44516</v>
+        <v>44476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3731,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3774,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3788,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45446</v>
+        <v>45975</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3803,13 +3783,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3852,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3866,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45188</v>
+        <v>45000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3881,8 +3856,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3925,7 +3905,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3935,14 +3915,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45211</v>
+        <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3954,8 +3934,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3998,7 +3983,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4012,10 +3997,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45272</v>
+        <v>44516</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4028,7 +4013,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4071,7 +4056,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4085,10 +4070,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45448</v>
+        <v>44972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4101,7 +4086,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4144,7 +4129,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4158,10 +4143,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46153</v>
+        <v>44972</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4173,13 +4158,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>8.5</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4222,7 +4202,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4236,10 +4216,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45679</v>
+        <v>46153</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4251,8 +4231,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4295,7 +4280,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4309,10 +4294,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46161</v>
+        <v>45188</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4324,13 +4309,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4353,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4367,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46162</v>
+        <v>45197</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4404,11 +4384,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4451,7 +4431,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4465,10 +4445,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4486,7 +4466,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4529,7 +4509,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4543,10 +4523,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44812</v>
+        <v>46162</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4558,8 +4538,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4602,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4616,10 +4601,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45588</v>
+        <v>44790</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4632,7 +4617,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4675,7 +4660,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4689,10 +4674,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44972</v>
+        <v>44727</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4705,7 +4690,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4748,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4762,10 +4747,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46244</v>
+        <v>46162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4777,8 +4762,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4821,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4835,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46204</v>
+        <v>45282</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4850,13 +4840,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4899,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4913,10 +4898,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46204</v>
+        <v>46044</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4928,13 +4913,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4977,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4991,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46132</v>
+        <v>45095</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5007,7 +4987,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5050,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5064,10 +5044,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46205</v>
+        <v>45588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5079,13 +5059,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5128,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5142,10 +5117,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46205</v>
+        <v>44972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5157,13 +5132,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5206,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5220,10 +5190,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46205</v>
+        <v>44967</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5235,8 +5205,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5279,7 +5254,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5293,10 +5268,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46205</v>
+        <v>45272</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5309,7 +5284,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5352,7 +5327,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5366,10 +5341,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45631</v>
+        <v>46244</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5382,7 +5357,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5425,7 +5400,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5439,10 +5414,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46259</v>
+        <v>45471</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5454,13 +5429,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5503,7 +5473,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5517,10 +5487,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46272</v>
+        <v>46204</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5532,8 +5502,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5576,7 +5551,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5590,10 +5565,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45282</v>
+        <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5606,7 +5581,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5649,7 +5624,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5663,10 +5638,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45181</v>
+        <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5679,7 +5654,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5722,7 +5697,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5736,10 +5711,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44782</v>
+        <v>45420</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5752,7 +5727,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5795,7 +5770,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5809,10 +5784,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44727</v>
+        <v>44636</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5825,7 +5800,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5868,7 +5843,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5882,10 +5857,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44476</v>
+        <v>46204</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5897,8 +5872,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>6.7</v>
+        <v>9.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5941,7 +5921,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5955,10 +5935,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44972</v>
+        <v>46205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5970,8 +5950,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6014,7 +5999,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6028,10 +6013,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45420</v>
+        <v>46205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6043,8 +6028,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6087,7 +6077,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6101,10 +6091,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45188</v>
+        <v>46132</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6117,7 +6107,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6160,7 +6150,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6174,10 +6164,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44972</v>
+        <v>45699</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6189,8 +6179,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6233,7 +6228,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6247,10 +6242,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45471</v>
+        <v>45628</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6262,8 +6257,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6306,7 +6306,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45251</v>
+        <v>46259</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6335,8 +6335,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6396,7 +6401,7 @@
         <v>45387</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6457,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6474,7 +6479,7 @@
         <v>45251</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6487,7 +6492,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6530,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6544,10 +6549,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44951</v>
+        <v>45251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6560,7 +6565,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6617,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45771</v>
+        <v>45744</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6633,7 +6638,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6676,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6690,10 +6695,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44957</v>
+        <v>45188</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6706,7 +6711,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45234</v>
+        <v>46272</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6779,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6822,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6836,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44967</v>
+        <v>45251</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6851,13 +6856,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45744</v>
+        <v>45679</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45699</v>
+        <v>45783</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7002,13 +7002,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44636</v>
+        <v>45644</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7076,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7133,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45628</v>
+        <v>45812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7155,11 +7150,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45783</v>
+        <v>45827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7231,8 +7226,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7509,7 +7509,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7679,10 +7679,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18303-2022</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44685</v>
+        <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1563,13 +1563,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 18303-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45181</v>
+        <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1639,6 +1634,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44648</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45771</v>
+        <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,8 +1860,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45448</v>
+        <v>45644</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1939,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44812</v>
+        <v>45812</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2006,8 +2011,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2060,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2074,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45446</v>
+        <v>45095</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2079,13 +2089,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44951</v>
+        <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2157,8 +2162,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44957</v>
+        <v>45903</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2231,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2288,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45234</v>
+        <v>45000</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2303,8 +2313,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2347,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2361,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45631</v>
+        <v>45919</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2377,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2420,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2434,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45903</v>
+        <v>45926</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2449,8 +2464,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2493,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2503,14 +2523,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45211</v>
+        <v>44790</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2523,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2566,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2580,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45919</v>
+        <v>45000</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2595,8 +2615,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2639,7 +2664,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2653,10 +2678,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45926</v>
+        <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2668,13 +2693,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2717,7 +2737,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2731,10 +2751,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46132</v>
+        <v>44972</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2747,7 +2767,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2790,7 +2810,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2804,10 +2824,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46132</v>
+        <v>45958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2820,7 +2840,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2863,7 +2883,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2877,10 +2897,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46132</v>
+        <v>45960</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2893,7 +2913,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2936,7 +2956,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2950,10 +2970,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45000</v>
+        <v>45968</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2965,13 +2985,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3014,7 +3029,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3028,10 +3043,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45958</v>
+        <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3043,8 +3058,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3087,7 +3107,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3101,10 +3121,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44782</v>
+        <v>45216</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3117,7 +3137,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3160,7 +3180,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3174,10 +3194,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45960</v>
+        <v>45975</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3190,7 +3210,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3233,7 +3253,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3247,10 +3267,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45251</v>
+        <v>45980</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3262,8 +3282,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3306,7 +3331,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3320,10 +3345,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45716</v>
+        <v>45446</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3335,8 +3360,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3379,7 +3409,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3393,10 +3423,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45968</v>
+        <v>45188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3409,7 +3439,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3452,7 +3482,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3462,14 +3492,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44972</v>
+        <v>45211</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3482,7 +3512,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3525,7 +3555,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3539,10 +3569,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45827</v>
+        <v>45272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3554,13 +3584,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3603,7 +3628,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3617,10 +3642,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45973</v>
+        <v>45448</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3632,13 +3657,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3701,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3715,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44476</v>
+        <v>45679</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3731,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.7</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3774,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3788,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45975</v>
+        <v>44812</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3804,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45000</v>
+        <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3856,13 +3876,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3905,7 +3920,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3919,10 +3934,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45980</v>
+        <v>46132</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3934,13 +3949,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3983,7 +3993,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44516</v>
+        <v>46132</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4013,7 +4023,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4056,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4070,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44972</v>
+        <v>46132</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4086,7 +4096,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4129,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4143,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44972</v>
+        <v>45716</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4159,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4202,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4216,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46153</v>
+        <v>45631</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4231,13 +4241,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4280,7 +4285,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4294,10 +4299,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45188</v>
+        <v>45827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4309,8 +4314,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4353,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4367,10 +4377,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45197</v>
+        <v>44516</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4382,13 +4392,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4431,7 +4436,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4445,10 +4450,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46161</v>
+        <v>45282</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4460,13 +4465,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46162</v>
+        <v>45181</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4538,13 +4538,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4582,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4601,10 +4596,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44790</v>
+        <v>44782</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4617,7 +4612,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4677,7 +4672,7 @@
         <v>44727</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4733,7 +4728,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4742,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4764,11 +4759,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>8.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4806,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4820,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45282</v>
+        <v>44476</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4841,7 +4836,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4884,7 +4879,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4898,10 +4893,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46044</v>
+        <v>46161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4913,8 +4908,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4957,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45095</v>
+        <v>46162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4986,8 +4986,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5030,7 +5035,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5044,10 +5049,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45588</v>
+        <v>46162</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5059,8 +5064,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5120,7 +5130,7 @@
         <v>44972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5176,7 +5186,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5190,10 +5200,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44967</v>
+        <v>45588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5205,13 +5215,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5254,7 +5259,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5268,10 +5273,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45272</v>
+        <v>45420</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5284,7 +5289,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46244</v>
+        <v>45188</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45471</v>
+        <v>44972</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46204</v>
+        <v>45471</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5502,13 +5507,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5653,8 +5653,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>9.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5697,7 +5702,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5711,10 +5716,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45420</v>
+        <v>45251</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5727,7 +5732,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5770,7 +5775,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5784,10 +5789,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44636</v>
+        <v>46204</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5799,8 +5804,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5843,7 +5853,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5857,10 +5867,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46204</v>
+        <v>46132</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5872,13 +5882,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5921,7 +5926,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5931,14 +5936,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46205</v>
+        <v>45387</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5956,7 +5961,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5999,7 +6004,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6016,7 +6021,7 @@
         <v>46205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6034,7 +6039,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6077,7 +6082,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6091,10 +6096,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46132</v>
+        <v>46205</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6106,8 +6111,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6150,7 +6160,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6164,10 +6174,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45699</v>
+        <v>46205</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6179,13 +6189,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6228,7 +6233,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6242,10 +6247,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45628</v>
+        <v>46205</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6257,13 +6262,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6306,7 +6306,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46259</v>
+        <v>45251</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6335,13 +6335,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6379,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6394,14 +6389,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45387</v>
+        <v>46259</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6419,7 +6414,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6476,10 +6471,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45251</v>
+        <v>44951</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6492,7 +6487,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6549,10 +6544,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6565,7 +6560,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45744</v>
+        <v>44957</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6638,7 +6633,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6695,10 +6690,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45188</v>
+        <v>45234</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6711,7 +6706,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46272</v>
+        <v>44967</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6783,8 +6778,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45251</v>
+        <v>45744</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45679</v>
+        <v>45699</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6929,8 +6929,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6978,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6992,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45783</v>
+        <v>46272</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +7008,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7051,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7065,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45644</v>
+        <v>44636</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7076,7 +7081,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45812</v>
+        <v>45628</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7150,11 +7155,11 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45827</v>
+        <v>45783</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7226,13 +7231,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7509,7 +7509,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7679,10 +7679,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45197</v>
+        <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,13 +1860,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1909,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45644</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1938,8 +1933,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45812</v>
+        <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,13 +2011,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2060,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45095</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2090,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2133,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45827</v>
+        <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2162,13 +2157,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45903</v>
+        <v>45827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2240,8 +2230,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2301,7 +2296,7 @@
         <v>45000</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2362,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45919</v>
+        <v>44782</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2392,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45926</v>
+        <v>45251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2464,13 +2459,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44790</v>
+        <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2533,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2603,7 +2593,7 @@
         <v>45000</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2664,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2678,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46044</v>
+        <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2694,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2737,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2754,7 +2744,7 @@
         <v>44972</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2767,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2810,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2824,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45958</v>
+        <v>46132</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2840,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2883,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2897,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45960</v>
+        <v>46132</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2913,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2956,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2970,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45968</v>
+        <v>46132</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2986,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3029,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3043,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45973</v>
+        <v>45903</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3058,13 +3048,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3107,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3121,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45216</v>
+        <v>45188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3137,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3180,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3194,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45975</v>
+        <v>45919</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3210,7 +3195,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3253,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3267,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45980</v>
+        <v>45197</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3284,11 +3269,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3331,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3345,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45446</v>
+        <v>45926</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3366,7 +3351,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3409,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3423,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45188</v>
+        <v>45716</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3439,7 +3424,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3482,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,14 +3477,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45211</v>
+        <v>44790</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3512,7 +3497,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3555,7 +3540,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3569,10 +3554,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45272</v>
+        <v>45827</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3584,8 +3569,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3628,7 +3618,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3642,10 +3632,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45448</v>
+        <v>44516</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3658,7 +3648,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3701,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3715,10 +3705,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45679</v>
+        <v>45095</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3731,7 +3721,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3774,7 +3764,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3788,10 +3778,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44812</v>
+        <v>46153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3803,8 +3793,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>8.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3847,7 +3842,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3864,7 +3859,7 @@
         <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3877,7 +3872,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3920,7 +3915,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3934,10 +3929,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3949,8 +3944,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46132</v>
+        <v>46162</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4022,8 +4022,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4066,7 +4071,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4085,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46132</v>
+        <v>46162</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4095,8 +4100,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4149,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4163,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45716</v>
+        <v>44967</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4168,8 +4178,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4212,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4226,10 +4241,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45631</v>
+        <v>45272</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4242,7 +4257,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45827</v>
+        <v>45471</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4314,13 +4329,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4377,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44516</v>
+        <v>45588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4393,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4450,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45282</v>
+        <v>45958</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4466,7 +4476,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4509,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4523,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45181</v>
+        <v>45960</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4539,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4582,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4596,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44782</v>
+        <v>45968</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4612,7 +4622,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4655,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4669,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44727</v>
+        <v>46244</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4685,7 +4695,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4728,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4742,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46153</v>
+        <v>45973</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4763,7 +4773,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4806,7 +4816,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4820,10 +4830,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44476</v>
+        <v>45628</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4835,8 +4845,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4879,7 +4894,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4893,10 +4908,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46161</v>
+        <v>45975</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4908,13 +4923,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4957,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4981,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46162</v>
+        <v>45980</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4992,7 +5002,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5035,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5049,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46162</v>
+        <v>46204</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5066,11 +5076,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5123,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5137,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44972</v>
+        <v>46205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5143,7 +5153,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5186,7 +5196,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5200,10 +5210,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45588</v>
+        <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5259,7 +5269,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5273,10 +5283,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45420</v>
+        <v>46204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5288,8 +5298,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5332,7 +5347,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5346,10 +5361,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45188</v>
+        <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5361,8 +5376,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5405,7 +5425,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5419,10 +5439,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44972</v>
+        <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5434,8 +5454,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5478,7 +5503,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5492,10 +5517,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45471</v>
+        <v>46132</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5508,7 +5533,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5551,7 +5576,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5565,10 +5590,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46244</v>
+        <v>45181</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5581,7 +5606,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5624,7 +5649,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5638,10 +5663,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46204</v>
+        <v>45448</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5653,13 +5678,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>9.4</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5702,7 +5722,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5716,10 +5736,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45251</v>
+        <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5731,8 +5751,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5775,7 +5800,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5789,10 +5814,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46204</v>
+        <v>45631</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5804,13 +5829,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5853,7 +5873,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5867,10 +5887,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46132</v>
+        <v>46272</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5883,7 +5903,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5926,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5936,14 +5956,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45387</v>
+        <v>45211</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5953,11 +5973,6 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -6004,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6018,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46205</v>
+        <v>44476</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6033,13 +6048,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6082,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6096,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46205</v>
+        <v>44727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6111,13 +6121,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6160,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6174,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46205</v>
+        <v>45282</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6190,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6233,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6247,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46205</v>
+        <v>46044</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6263,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6306,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6320,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45251</v>
+        <v>45420</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6336,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6379,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6393,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46259</v>
+        <v>44636</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6408,13 +6413,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44951</v>
+        <v>45699</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6486,8 +6486,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6530,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6540,14 +6545,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45771</v>
+        <v>45387</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6559,8 +6564,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6613,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6617,10 +6627,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44957</v>
+        <v>45251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6676,7 +6686,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6690,10 +6700,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45234</v>
+        <v>45251</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6706,7 +6716,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6759,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6773,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44967</v>
+        <v>45744</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6778,13 +6788,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6832,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6846,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45744</v>
+        <v>45188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6862,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6905,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6919,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45699</v>
+        <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6929,13 +6934,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6978,7 +6978,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46272</v>
+        <v>45679</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7051,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44636</v>
+        <v>45783</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45628</v>
+        <v>45644</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,13 +7153,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45783</v>
+        <v>45812</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7231,8 +7226,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7509,7 +7509,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7679,10 +7679,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45771</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44812</v>
+        <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,8 +1860,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>45095</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1933,13 +1938,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44951</v>
+        <v>45000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,8 +2011,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2060,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2090,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45234</v>
+        <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2157,8 +2162,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45827</v>
+        <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2230,13 +2240,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2279,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45000</v>
+        <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2308,13 +2313,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44782</v>
+        <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2386,8 +2386,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45251</v>
+        <v>45446</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2459,8 +2464,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44972</v>
+        <v>44516</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45000</v>
+        <v>45188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2605,13 +2615,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2664,14 +2669,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44972</v>
+        <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44972</v>
+        <v>45903</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46132</v>
+        <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46132</v>
+        <v>45272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46132</v>
+        <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2975,8 +2980,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3029,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3043,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45903</v>
+        <v>45448</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3059,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3102,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3116,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45188</v>
+        <v>45679</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3132,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3175,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3189,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45919</v>
+        <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3205,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3248,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3262,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45197</v>
+        <v>44972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3267,13 +3277,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3321,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3335,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45926</v>
+        <v>46153</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3351,7 +3356,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45716</v>
+        <v>45958</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>7.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3467,7 +3472,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44790</v>
+        <v>45960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3497,7 +3502,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3540,7 +3545,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45827</v>
+        <v>45631</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3569,13 +3574,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44516</v>
+        <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45095</v>
+        <v>45973</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3720,8 +3720,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3764,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3778,10 +3783,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46153</v>
+        <v>45975</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3793,13 +3798,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44972</v>
+        <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3871,8 +3871,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3932,7 +3937,7 @@
         <v>46161</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3993,7 +3998,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4007,10 +4012,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46162</v>
+        <v>45282</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4022,13 +4027,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46162</v>
+        <v>45181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4100,13 +4100,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4149,7 +4144,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4163,10 +4158,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44967</v>
+        <v>46162</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4180,11 +4175,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4241,10 +4236,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45272</v>
+        <v>46162</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4256,8 +4251,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45471</v>
+        <v>44782</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45588</v>
+        <v>44727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45958</v>
+        <v>44476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45960</v>
+        <v>46044</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45968</v>
+        <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4665,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46244</v>
+        <v>45588</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45973</v>
+        <v>45420</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4767,13 +4767,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4816,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4830,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45628</v>
+        <v>45188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4845,13 +4840,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4894,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4908,10 +4898,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45975</v>
+        <v>44972</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4924,7 +4914,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45980</v>
+        <v>45471</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4996,13 +4986,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5044,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46204</v>
+        <v>45251</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5074,13 +5059,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5123,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5137,10 +5117,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5153,7 +5133,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5196,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5206,14 +5186,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46205</v>
+        <v>45387</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5225,8 +5205,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5286,7 +5271,7 @@
         <v>46204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5347,7 +5332,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5361,10 +5346,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5376,13 +5361,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5425,7 +5405,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5439,10 +5419,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5454,13 +5434,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5503,7 +5478,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5520,7 +5495,7 @@
         <v>46132</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5533,7 +5508,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5576,7 +5551,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5590,10 +5565,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45181</v>
+        <v>45716</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5606,7 +5581,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5649,7 +5624,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5663,10 +5638,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45448</v>
+        <v>45251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5679,7 +5654,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5722,7 +5697,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5736,10 +5711,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46259</v>
+        <v>46204</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5757,7 +5732,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5800,7 +5775,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5814,10 +5789,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45631</v>
+        <v>46132</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5830,7 +5805,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5873,7 +5848,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5887,10 +5862,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46272</v>
+        <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5902,8 +5877,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5926,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5956,14 +5936,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45211</v>
+        <v>44951</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5976,7 +5956,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +5999,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6013,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44476</v>
+        <v>46205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6048,8 +6028,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>6.7</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6077,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6091,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44727</v>
+        <v>46205</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6122,7 +6107,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6150,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6164,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45282</v>
+        <v>46205</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6180,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6223,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6237,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46044</v>
+        <v>45771</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6253,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6296,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6310,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45420</v>
+        <v>44957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6326,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6369,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6383,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44636</v>
+        <v>45234</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6399,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6442,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6456,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45699</v>
+        <v>44967</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6488,11 +6473,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6520,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6545,14 +6530,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45387</v>
+        <v>46259</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6570,7 +6555,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6613,7 +6598,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6627,10 +6612,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45251</v>
+        <v>45744</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6643,7 +6628,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6686,7 +6671,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6700,10 +6685,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45251</v>
+        <v>45699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6715,8 +6700,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6759,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6773,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45744</v>
+        <v>44636</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6789,7 +6779,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6832,7 +6822,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6846,10 +6836,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45188</v>
+        <v>45628</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6861,8 +6851,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6905,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6919,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45251</v>
+        <v>45783</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6935,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6978,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6992,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45679</v>
+        <v>46272</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7008,7 +7003,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45783</v>
+        <v>45644</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7076,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7133,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45644</v>
+        <v>45812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,8 +7148,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45812</v>
+        <v>45827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7228,11 +7228,11 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7509,7 +7509,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7679,10 +7679,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7760,7 +7760,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>45095</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45446</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>44516</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>45188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45211</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45903</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45448</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45679</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>44972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>46153</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45958</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>45960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>45631</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>45973</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45975</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>46161</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45282</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>45181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>46162</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>46162</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44782</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44727</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44476</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>46044</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>45588</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45420</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>45188</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>44972</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45471</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45251</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>46244</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45387</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>46204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46132</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>46132</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>46132</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45716</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>46204</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>46132</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44951</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>46205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>46205</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>46205</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45771</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45234</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44967</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>46259</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45744</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44636</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45628</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45783</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>46272</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>45644</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45266</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44901</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44606</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE96"/>
+  <dimension ref="A1:AE98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>45095</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45216</v>
+        <v>45716</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45827</v>
+        <v>45216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2386,13 +2386,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45446</v>
+        <v>45827</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2470,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44516</v>
+        <v>45903</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2543,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45188</v>
+        <v>45919</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2616,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2669,14 +2664,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45211</v>
+        <v>44516</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45903</v>
+        <v>45926</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2761,8 +2756,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45919</v>
+        <v>45446</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2834,8 +2834,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2883,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2897,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45272</v>
+        <v>45188</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2913,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2956,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2970,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45926</v>
+        <v>46153</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2986,7 +2991,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3029,7 +3034,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3039,14 +3044,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45448</v>
+        <v>45211</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3059,7 +3064,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3102,7 +3107,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3116,10 +3121,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45679</v>
+        <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3132,7 +3137,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3175,7 +3180,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3189,10 +3194,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44812</v>
+        <v>46161</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3204,8 +3209,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3248,7 +3258,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3262,10 +3272,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44972</v>
+        <v>45958</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3278,7 +3288,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>7.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3331,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3345,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46153</v>
+        <v>45960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3350,13 +3360,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3399,7 +3404,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3413,10 +3418,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45958</v>
+        <v>45448</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3429,7 +3434,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3472,7 +3477,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3486,10 +3491,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45960</v>
+        <v>46162</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3501,8 +3506,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3545,7 +3555,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3559,10 +3569,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45631</v>
+        <v>45968</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3575,7 +3585,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3618,7 +3628,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3632,10 +3642,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45968</v>
+        <v>46162</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3647,8 +3657,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3708,7 +3723,7 @@
         <v>45973</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3769,7 +3784,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3798,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45975</v>
+        <v>45679</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3799,7 +3814,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3842,7 +3857,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3856,10 +3871,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45980</v>
+        <v>45975</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3871,13 +3886,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3920,7 +3930,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3934,10 +3944,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46161</v>
+        <v>45980</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3955,7 +3965,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3998,7 +4008,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4012,10 +4022,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45282</v>
+        <v>44812</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4028,7 +4038,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4071,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4085,10 +4095,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45181</v>
+        <v>44972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4101,7 +4111,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4144,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4158,10 +4168,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46162</v>
+        <v>45631</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4173,13 +4183,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4222,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4236,10 +4241,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46162</v>
+        <v>45588</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4251,13 +4256,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44782</v>
+        <v>46044</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44727</v>
+        <v>45282</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44476</v>
+        <v>45181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.7</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46044</v>
+        <v>44782</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44972</v>
+        <v>44727</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4665,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45588</v>
+        <v>44476</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>6.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45420</v>
+        <v>46204</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4767,8 +4767,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4816,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4830,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45188</v>
+        <v>46204</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4840,8 +4845,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4884,7 +4894,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4898,10 +4908,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44972</v>
+        <v>46132</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4914,7 +4924,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4957,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4981,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45471</v>
+        <v>46132</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4987,7 +4997,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5030,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5044,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45251</v>
+        <v>46132</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5060,7 +5070,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5117,10 +5127,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5132,8 +5142,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5176,7 +5191,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5186,14 +5201,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45387</v>
+        <v>46132</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5205,13 +5220,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5254,7 +5264,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5268,10 +5278,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46204</v>
+        <v>44972</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5283,13 +5293,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>9.4</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5332,7 +5337,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5346,10 +5351,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46132</v>
+        <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5361,8 +5366,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5405,7 +5415,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5419,10 +5429,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46132</v>
+        <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5435,7 +5445,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5478,7 +5488,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5492,10 +5502,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46132</v>
+        <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5508,7 +5518,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5551,7 +5561,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5565,10 +5575,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45716</v>
+        <v>45420</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5581,7 +5591,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5624,7 +5634,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5638,10 +5648,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45251</v>
+        <v>45188</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5654,7 +5664,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5697,7 +5707,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5711,10 +5721,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46204</v>
+        <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5732,7 +5742,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5775,7 +5785,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5789,10 +5799,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46132</v>
+        <v>44972</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5805,7 +5815,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5848,7 +5858,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5862,10 +5872,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46205</v>
+        <v>45471</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5877,13 +5887,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5926,7 +5931,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5940,10 +5945,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44951</v>
+        <v>45251</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5956,7 +5961,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5999,7 +6004,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6009,14 +6014,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46205</v>
+        <v>45387</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6034,7 +6039,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6077,7 +6082,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6091,10 +6096,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46205</v>
+        <v>46272</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6107,7 +6112,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6150,7 +6155,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6164,10 +6169,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46205</v>
+        <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6180,7 +6185,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6223,7 +6228,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6237,10 +6242,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45771</v>
+        <v>44951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6253,7 +6258,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6296,7 +6301,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6310,10 +6315,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44957</v>
+        <v>45771</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6326,7 +6331,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6369,7 +6374,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6383,10 +6388,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45234</v>
+        <v>44957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6399,7 +6404,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6442,7 +6447,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6456,10 +6461,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44967</v>
+        <v>45234</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6471,13 +6476,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46259</v>
+        <v>44967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
         <v>45744</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44636</v>
+        <v>46287</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6778,8 +6778,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6822,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6836,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45628</v>
+        <v>46244</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6851,13 +6856,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45783</v>
+        <v>46286</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46272</v>
+        <v>44636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45644</v>
+        <v>45628</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7075,8 +7075,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7119,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45812</v>
+        <v>45783</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7148,13 +7153,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45827</v>
+        <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7226,13 +7226,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,24 +7270,24 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45266</v>
+        <v>45812</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7306,11 +7301,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>12.5</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,24 +7348,24 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45266</v>
+        <v>45827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7388,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7431,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7445,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7466,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7509,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7523,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7544,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7587,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7601,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7622,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>54.4</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7665,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7679,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44606</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7700,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7740,10 +7735,10 @@
       </c>
       <c r="V95" s="2" t="inlineStr"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4416-2023</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7760,7 +7755,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7778,45 +7773,201 @@
         </is>
       </c>
       <c r="I96" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>S 923-2022</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>44606</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>S 4416-2023</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
         <v>40</v>
       </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" s="2" t="inlineStr"/>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45188</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45095</v>
+        <v>44790</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45000</v>
+        <v>45216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,13 +2011,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2060,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44790</v>
+        <v>45095</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2090,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2133,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45000</v>
+        <v>44812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2162,13 +2157,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44972</v>
+        <v>45446</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2240,8 +2230,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2279,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2293,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45716</v>
+        <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2309,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2352,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2366,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45216</v>
+        <v>44951</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2382,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45827</v>
+        <v>44957</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2459,13 +2454,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2525,7 +2515,7 @@
         <v>45903</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2581,7 +2571,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2585,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45919</v>
+        <v>45234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2601,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2644,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2658,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44516</v>
+        <v>44967</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2683,8 +2673,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2722,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2736,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45926</v>
+        <v>45272</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2756,13 +2751,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2795,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2809,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45446</v>
+        <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2834,13 +2824,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2883,7 +2868,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2897,10 +2882,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45188</v>
+        <v>45471</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2913,7 +2898,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2956,7 +2941,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2970,10 +2955,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46153</v>
+        <v>45926</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2991,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3034,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3044,14 +3029,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45211</v>
+        <v>45644</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3064,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3107,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3121,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45272</v>
+        <v>45812</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3136,8 +3121,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3180,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3194,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46161</v>
+        <v>45958</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3209,13 +3199,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>7.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3258,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3272,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45958</v>
+        <v>45000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3287,8 +3272,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3348,7 +3338,7 @@
         <v>45960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3404,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3418,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45448</v>
+        <v>45628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3433,8 +3423,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3477,7 +3472,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46162</v>
+        <v>44782</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3506,13 +3501,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3572,7 +3562,7 @@
         <v>45968</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3628,7 +3618,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3642,10 +3632,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46162</v>
+        <v>45973</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3659,11 +3649,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3706,7 +3696,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3720,10 +3710,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45973</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3735,13 +3725,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3784,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3798,10 +3783,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45679</v>
+        <v>45975</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3814,7 +3799,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3857,7 +3842,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3871,10 +3856,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45975</v>
+        <v>45980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3886,8 +3871,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3930,7 +3920,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3944,10 +3934,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45980</v>
+        <v>44972</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3959,13 +3949,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4008,7 +3993,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4022,10 +4007,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44812</v>
+        <v>45181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4038,7 +4023,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4081,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4095,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44972</v>
+        <v>45000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4110,8 +4095,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4154,7 +4144,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4168,10 +4158,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45631</v>
+        <v>44972</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4184,7 +4174,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4217,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4241,10 +4231,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45588</v>
+        <v>44972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4257,7 +4247,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4290,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4304,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46044</v>
+        <v>45827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4329,8 +4319,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4368,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4382,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45282</v>
+        <v>45448</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4398,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4441,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4455,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45181</v>
+        <v>46044</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4476,7 +4471,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44782</v>
+        <v>45631</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4549,7 +4544,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4602,14 +4597,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44727</v>
+        <v>45211</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4622,7 +4617,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4665,7 +4660,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4679,10 +4674,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44476</v>
+        <v>46286</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4695,7 +4690,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4747,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46204</v>
+        <v>46244</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4767,13 +4762,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4816,7 +4806,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4830,10 +4820,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46204</v>
+        <v>46287</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4851,7 +4841,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4894,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4908,10 +4898,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46132</v>
+        <v>44476</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4924,7 +4914,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46132</v>
+        <v>44727</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4997,7 +4987,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5040,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5044,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46132</v>
+        <v>45282</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5070,7 +5060,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5117,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5142,13 +5132,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5191,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5208,7 +5193,7 @@
         <v>46132</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5221,7 +5206,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5264,7 +5249,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5278,10 +5263,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44972</v>
+        <v>46132</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5294,7 +5279,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5337,7 +5322,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5351,10 +5336,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46205</v>
+        <v>45420</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5366,13 +5351,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5415,7 +5395,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5429,10 +5409,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46205</v>
+        <v>44636</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5445,7 +5425,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5488,7 +5468,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5502,10 +5482,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46205</v>
+        <v>45699</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5517,8 +5497,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5561,7 +5546,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5571,14 +5556,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45420</v>
+        <v>45387</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5590,8 +5575,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5634,7 +5624,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5648,10 +5638,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45188</v>
+        <v>45251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5664,7 +5654,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5707,7 +5697,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5721,10 +5711,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46259</v>
+        <v>45251</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5736,13 +5726,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5785,7 +5770,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5799,10 +5784,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44972</v>
+        <v>45744</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5815,7 +5800,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5858,7 +5843,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5872,10 +5857,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45471</v>
+        <v>45716</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5888,7 +5873,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5931,7 +5916,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5945,10 +5930,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45251</v>
+        <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5961,7 +5946,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6004,7 +5989,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6014,14 +5999,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45387</v>
+        <v>45827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6024,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6082,7 +6067,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6096,10 +6081,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46272</v>
+        <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6097,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6155,7 +6140,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6172,7 +6157,7 @@
         <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6170,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6228,7 +6213,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6242,10 +6227,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44951</v>
+        <v>45679</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6258,7 +6243,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6301,7 +6286,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6315,10 +6300,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45771</v>
+        <v>46153</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6330,8 +6315,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>8.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6374,7 +6364,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6388,10 +6378,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44957</v>
+        <v>45783</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6404,7 +6394,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6447,7 +6437,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6461,10 +6451,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45234</v>
+        <v>46161</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6476,8 +6466,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6520,7 +6515,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6534,10 +6529,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44967</v>
+        <v>46162</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6551,11 +6546,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6598,7 +6593,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6612,10 +6607,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45744</v>
+        <v>46162</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6625,6 +6620,11 @@
       <c r="G81" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -6671,7 +6671,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45699</v>
+        <v>45588</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6700,13 +6700,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6744,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6758,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46287</v>
+        <v>46204</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6779,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6822,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6836,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6852,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6895,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6909,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46286</v>
+        <v>46205</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6925,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6968,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6982,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44636</v>
+        <v>46204</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7002,8 +6997,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45628</v>
+        <v>46205</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45783</v>
+        <v>46205</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,8 +7153,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45644</v>
+        <v>46132</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7227,7 +7232,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7270,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7284,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45812</v>
+        <v>46259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7301,11 +7306,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7348,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7362,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45827</v>
+        <v>46272</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7377,13 +7382,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45188</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45771</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44790</v>
+        <v>45095</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45216</v>
+        <v>45000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,8 +2011,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2060,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45095</v>
+        <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2090,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44812</v>
+        <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2157,8 +2162,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45446</v>
+        <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2230,13 +2240,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2279,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44972</v>
+        <v>45716</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2309,7 +2314,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2352,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2366,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44951</v>
+        <v>45216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2382,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2425,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44957</v>
+        <v>45903</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2455,7 +2460,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45903</v>
+        <v>45919</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2528,7 +2533,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2571,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2585,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45234</v>
+        <v>45926</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2600,8 +2605,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2644,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2658,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44967</v>
+        <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2679,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2722,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2736,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45272</v>
+        <v>45188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2752,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2795,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2805,14 +2815,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45919</v>
+        <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2825,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2868,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2882,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45471</v>
+        <v>45827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2897,8 +2907,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2941,7 +2956,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2955,10 +2970,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45926</v>
+        <v>45272</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2970,13 +2985,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3029,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3043,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45644</v>
+        <v>45448</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3059,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3102,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3116,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45812</v>
+        <v>44516</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3121,13 +3131,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3187,7 +3192,7 @@
         <v>45958</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3243,7 +3248,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3262,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45000</v>
+        <v>45679</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3272,13 +3277,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
         <v>45960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45628</v>
+        <v>45968</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3423,13 +3423,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3472,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44782</v>
+        <v>45973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3501,8 +3496,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45973</v>
+        <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3647,13 +3647,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3696,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3726,7 +3721,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3764,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3778,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45975</v>
+        <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3798,8 +3793,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45980</v>
+        <v>46153</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3873,11 +3873,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44972</v>
+        <v>45631</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45181</v>
+        <v>46161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4022,8 +4022,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4066,7 +4071,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4085,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45000</v>
+        <v>46162</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4097,11 +4102,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4144,7 +4149,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4158,10 +4163,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44972</v>
+        <v>45282</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4174,7 +4179,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4217,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4231,10 +4236,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44972</v>
+        <v>46162</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4246,8 +4251,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4290,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4304,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45827</v>
+        <v>45181</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4319,13 +4329,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4368,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4382,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45448</v>
+        <v>44782</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4398,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4458,7 +4463,7 @@
         <v>46044</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4514,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45631</v>
+        <v>44727</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4544,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4597,14 +4602,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45211</v>
+        <v>44476</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4617,7 +4622,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4660,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4674,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46286</v>
+        <v>45588</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4690,7 +4695,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4733,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46244</v>
+        <v>44972</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4763,7 +4768,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4806,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4820,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46287</v>
+        <v>46132</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4835,13 +4840,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4884,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44476</v>
+        <v>46132</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.7</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4957,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44727</v>
+        <v>46132</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5030,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45282</v>
+        <v>45420</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46132</v>
+        <v>45188</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46132</v>
+        <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5205,8 +5205,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>9.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5249,7 +5254,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5263,10 +5268,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46132</v>
+        <v>46204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5278,8 +5283,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5322,7 +5332,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5336,10 +5346,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45420</v>
+        <v>46132</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5352,7 +5362,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5395,7 +5405,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5409,10 +5419,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44636</v>
+        <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5424,8 +5434,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5468,7 +5483,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5482,10 +5497,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45699</v>
+        <v>44972</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5497,13 +5512,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5546,7 +5556,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5556,14 +5566,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45387</v>
+        <v>45471</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5575,13 +5585,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5624,7 +5629,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5638,10 +5643,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45251</v>
+        <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5653,8 +5658,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5697,7 +5707,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5711,10 +5721,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45251</v>
+        <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5727,7 +5737,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5770,7 +5780,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45744</v>
+        <v>46205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5800,7 +5810,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5843,7 +5853,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5857,10 +5867,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45716</v>
+        <v>45251</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5873,7 +5883,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5916,7 +5926,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5926,14 +5936,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45188</v>
+        <v>45387</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5945,8 +5955,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5989,7 +6004,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6003,10 +6018,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45827</v>
+        <v>46259</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6024,7 +6039,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6067,7 +6082,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6081,10 +6096,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44516</v>
+        <v>45251</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6097,7 +6112,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6140,7 +6155,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6154,10 +6169,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45251</v>
+        <v>44951</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6170,7 +6185,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6213,7 +6228,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6227,10 +6242,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45679</v>
+        <v>45771</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6243,7 +6258,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6286,7 +6301,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6300,10 +6315,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46153</v>
+        <v>44957</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6315,13 +6330,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>8.5</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6364,7 +6374,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6378,10 +6388,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45783</v>
+        <v>45234</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6394,7 +6404,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6437,7 +6447,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6451,10 +6461,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46161</v>
+        <v>46272</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6466,13 +6476,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6515,7 +6520,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6529,10 +6534,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46162</v>
+        <v>44967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6546,11 +6551,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6593,7 +6598,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6607,10 +6612,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46162</v>
+        <v>45744</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6620,11 +6625,6 @@
       <c r="G81" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -6671,7 +6671,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45588</v>
+        <v>45699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6700,8 +6700,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6744,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6758,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46204</v>
+        <v>44636</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6773,13 +6778,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46205</v>
+        <v>45628</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6851,8 +6851,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6895,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6909,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46205</v>
+        <v>45783</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6925,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6968,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6982,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46204</v>
+        <v>46287</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +7008,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7051,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7065,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7075,13 +7080,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46205</v>
+        <v>46286</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,13 +7153,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46132</v>
+        <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7232,7 +7227,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7270,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7284,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46259</v>
+        <v>45812</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7306,11 +7301,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7348,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7362,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46272</v>
+        <v>45827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7382,8 +7377,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45197</v>
+        <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,13 +1860,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1909,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45095</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1938,8 +1933,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45000</v>
+        <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,13 +2011,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2060,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44790</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2090,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2133,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45000</v>
+        <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2162,13 +2157,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44972</v>
+        <v>46044</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,7 +2231,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45716</v>
+        <v>45903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2304,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2347,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2361,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45216</v>
+        <v>45919</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2377,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2420,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2434,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45903</v>
+        <v>45926</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2459,8 +2449,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2498,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2512,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45919</v>
+        <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2528,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2571,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2585,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45926</v>
+        <v>45000</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2606,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2649,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45446</v>
+        <v>44782</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2683,13 +2678,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2722,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2736,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45188</v>
+        <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2752,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2795,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2815,14 +2805,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45211</v>
+        <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2825,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2868,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2882,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45827</v>
+        <v>45251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2907,13 +2897,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2956,7 +2941,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2970,10 +2955,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45272</v>
+        <v>45812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2985,8 +2970,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3029,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3043,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45448</v>
+        <v>45968</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3059,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3102,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3116,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44516</v>
+        <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3132,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3175,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3189,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45958</v>
+        <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3204,8 +3194,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3248,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3262,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45679</v>
+        <v>46132</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3278,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45960</v>
+        <v>46132</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3351,7 +3346,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3394,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45968</v>
+        <v>45000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3423,8 +3418,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45973</v>
+        <v>46132</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3494,11 +3494,6 @@
       <c r="G39" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3562,7 +3557,7 @@
         <v>45975</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3618,7 +3613,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44812</v>
+        <v>45980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3647,8 +3642,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3708,7 +3708,7 @@
         <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45980</v>
+        <v>44972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3793,13 +3793,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3842,7 +3837,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3856,10 +3851,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46153</v>
+        <v>45188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3871,13 +3866,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3920,7 +3910,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3934,10 +3924,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45631</v>
+        <v>45716</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3950,7 +3940,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3993,7 +3983,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4007,10 +3997,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46161</v>
+        <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4024,11 +4014,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4071,7 +4061,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4085,10 +4075,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46162</v>
+        <v>45827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4102,11 +4092,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4149,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4163,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45282</v>
+        <v>44516</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4179,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4222,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4236,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46162</v>
+        <v>44790</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4251,13 +4241,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4285,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4299,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45181</v>
+        <v>45827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4329,8 +4314,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4377,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44782</v>
+        <v>46153</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4402,8 +4392,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>8.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4441,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4455,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46044</v>
+        <v>45095</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4476,7 +4471,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44727</v>
+        <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4548,8 +4543,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44476</v>
+        <v>46162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4621,8 +4621,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>6.7</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4665,7 +4670,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4679,10 +4684,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45588</v>
+        <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4695,7 +4700,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4743,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4757,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44972</v>
+        <v>46162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4767,8 +4772,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4835,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46132</v>
+        <v>44967</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4840,8 +4850,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4884,7 +4899,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4898,10 +4913,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46132</v>
+        <v>45272</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4914,7 +4929,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4957,7 +4972,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4971,10 +4986,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46132</v>
+        <v>45471</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4987,7 +5002,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5030,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5044,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45420</v>
+        <v>45588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5060,7 +5075,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5118,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5117,10 +5132,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45188</v>
+        <v>46204</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5132,8 +5147,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5176,7 +5196,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5190,10 +5210,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5205,13 +5225,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5254,7 +5269,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5268,10 +5283,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5283,13 +5298,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5332,7 +5342,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5346,10 +5356,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46132</v>
+        <v>46204</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5361,8 +5371,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5422,7 +5437,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5483,7 +5498,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5497,10 +5512,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44972</v>
+        <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5512,8 +5527,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5556,7 +5576,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5570,10 +5590,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45471</v>
+        <v>46132</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5586,7 +5606,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5629,7 +5649,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5643,10 +5663,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46205</v>
+        <v>45628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5664,7 +5684,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5707,7 +5727,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5721,10 +5741,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46205</v>
+        <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5736,8 +5756,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5780,7 +5805,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5794,10 +5819,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46205</v>
+        <v>45181</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5810,7 +5835,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5853,7 +5878,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5867,10 +5892,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45251</v>
+        <v>45448</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5883,7 +5908,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5926,7 +5951,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5936,14 +5961,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45387</v>
+        <v>46272</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5955,13 +5980,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6004,7 +6024,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6018,10 +6038,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46259</v>
+        <v>45631</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6033,13 +6053,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6082,7 +6097,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6092,14 +6107,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45251</v>
+        <v>45211</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6127,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6155,7 +6170,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6169,10 +6184,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44951</v>
+        <v>46286</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6185,7 +6200,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6228,7 +6243,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6242,10 +6257,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45771</v>
+        <v>46244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6258,7 +6273,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6301,7 +6316,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6315,10 +6330,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44957</v>
+        <v>44476</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6331,7 +6346,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6374,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6388,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45234</v>
+        <v>46287</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6403,8 +6418,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6447,7 +6467,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6461,10 +6481,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46272</v>
+        <v>44727</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6477,7 +6497,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6520,7 +6540,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6534,10 +6554,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44967</v>
+        <v>45282</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6549,13 +6569,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6598,7 +6613,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6612,10 +6627,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45744</v>
+        <v>45420</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6628,7 +6643,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6671,7 +6686,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6685,10 +6700,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45699</v>
+        <v>44636</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6700,13 +6715,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6759,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6773,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44636</v>
+        <v>45699</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6778,8 +6788,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6822,7 +6837,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6832,14 +6847,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45628</v>
+        <v>45387</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6872,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6915,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6929,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45783</v>
+        <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6945,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6988,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +7002,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46287</v>
+        <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7002,13 +7017,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7061,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7075,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46244</v>
+        <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7091,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7134,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7148,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46286</v>
+        <v>45188</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7154,7 +7164,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7207,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7221,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45644</v>
+        <v>45251</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7227,7 +7237,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7270,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7284,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45812</v>
+        <v>45679</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7299,13 +7309,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7348,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7362,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45827</v>
+        <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7377,13 +7382,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>46044</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45919</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45926</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45000</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44782</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>45251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45968</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>46132</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>46132</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>46132</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45975</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45716</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>44516</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44790</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>46153</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>45095</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>46162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>46162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44967</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>45272</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>45471</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>45588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>46204</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46204</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>46132</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45181</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45448</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>46272</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>45631</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45211</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>46286</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>46244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44476</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>46287</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44727</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45282</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45420</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44636</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45699</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45387</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>45188</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45251</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45679</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>46044</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45919</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>45926</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45000</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44782</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>45251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45812</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45968</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>46132</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>46132</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>46132</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>45975</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>45716</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45197</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>44516</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44790</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>46153</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>45095</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>46162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>46162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>44967</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>45272</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>45471</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>45588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>46204</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46204</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>46132</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45628</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>45181</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>45448</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>46272</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>45631</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45211</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>46286</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>46244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44476</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>46287</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44727</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45282</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>45420</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44636</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45699</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45387</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>45188</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>45251</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>45679</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45771</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44812</v>
+        <v>45644</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>45812</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44951</v>
+        <v>45903</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>45197</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2084,8 +2084,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45234</v>
+        <v>45919</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2158,7 +2163,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2206,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46044</v>
+        <v>45827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2230,8 +2235,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2288,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45903</v>
+        <v>45926</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2303,8 +2313,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2347,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2361,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45919</v>
+        <v>45095</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2377,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2420,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2434,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45926</v>
+        <v>45000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2455,7 +2470,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2513,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2527,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45644</v>
+        <v>45958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2528,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2571,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2585,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45000</v>
+        <v>45960</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2600,13 +2615,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44782</v>
+        <v>44790</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2679,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2722,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2736,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45958</v>
+        <v>45968</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2752,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2795,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2809,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45960</v>
+        <v>45000</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2824,8 +2834,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2868,7 +2883,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2882,10 +2897,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45251</v>
+        <v>45973</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2897,8 +2912,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2941,7 +2961,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2955,10 +2975,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45812</v>
+        <v>45975</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2970,13 +2990,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3034,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3048,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45968</v>
+        <v>45980</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3048,8 +3063,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3112,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3109,7 +3129,7 @@
         <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3122,7 +3142,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3185,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3199,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45973</v>
+        <v>46044</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3194,13 +3214,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3258,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3272,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46132</v>
+        <v>45216</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3273,7 +3288,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3331,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3345,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46132</v>
+        <v>45446</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3345,8 +3360,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3409,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3423,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45000</v>
+        <v>45188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3418,13 +3438,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3467,7 +3482,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3477,14 +3492,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46132</v>
+        <v>45211</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3497,7 +3512,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3540,7 +3555,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,10 +3569,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45975</v>
+        <v>45272</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3570,7 +3585,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3613,7 +3628,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3627,10 +3642,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45980</v>
+        <v>45448</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3642,13 +3657,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3691,7 +3701,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44972</v>
+        <v>45679</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3764,7 +3774,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3778,10 +3788,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44972</v>
+        <v>44812</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3794,7 +3804,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3837,7 +3847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45188</v>
+        <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3867,7 +3877,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3910,7 +3920,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45716</v>
+        <v>46132</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3940,7 +3950,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3983,7 +3993,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45197</v>
+        <v>46132</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4012,13 +4022,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4061,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4075,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45827</v>
+        <v>46132</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4090,13 +4095,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44516</v>
+        <v>45716</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44790</v>
+        <v>45631</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4302,7 +4302,7 @@
         <v>45827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46153</v>
+        <v>44516</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4392,13 +4392,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4441,7 +4436,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4455,10 +4450,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45095</v>
+        <v>45282</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4471,7 +4466,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4514,7 +4509,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4523,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46161</v>
+        <v>45181</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4543,13 +4538,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4582,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4606,10 +4596,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46162</v>
+        <v>44782</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4621,13 +4611,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4670,7 +4655,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4684,10 +4669,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44972</v>
+        <v>46153</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4699,8 +4684,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>8.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4743,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4757,10 +4747,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46162</v>
+        <v>44727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4772,13 +4762,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4821,7 +4806,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4835,10 +4820,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44967</v>
+        <v>44476</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4850,13 +4835,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>6.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4899,7 +4879,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4913,10 +4893,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45272</v>
+        <v>46161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4928,8 +4908,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4972,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4986,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45471</v>
+        <v>46162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5001,8 +4986,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5035,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5049,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45588</v>
+        <v>46162</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5074,8 +5064,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5118,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46204</v>
+        <v>44972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5147,13 +5142,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5196,7 +5186,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5210,10 +5200,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46205</v>
+        <v>45588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5226,7 +5216,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5269,7 +5259,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5283,10 +5273,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46205</v>
+        <v>45420</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5299,7 +5289,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5342,7 +5332,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5356,10 +5346,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46204</v>
+        <v>45188</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5371,13 +5361,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5420,7 +5405,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5434,10 +5419,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46205</v>
+        <v>44972</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5449,13 +5434,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5498,7 +5478,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5512,10 +5492,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46205</v>
+        <v>45471</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5527,13 +5507,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5576,7 +5551,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5590,10 +5565,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46132</v>
+        <v>46204</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5605,8 +5580,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5649,7 +5629,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5663,10 +5643,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45628</v>
+        <v>46204</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5684,7 +5664,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5727,7 +5707,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5741,10 +5721,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46259</v>
+        <v>45251</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5756,13 +5736,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5805,7 +5780,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5819,10 +5794,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45181</v>
+        <v>46205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5834,8 +5809,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5878,7 +5858,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5888,14 +5868,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45448</v>
+        <v>45387</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5907,8 +5887,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5951,7 +5936,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5965,10 +5950,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46272</v>
+        <v>46205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5980,8 +5965,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6024,7 +6014,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6038,10 +6028,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45631</v>
+        <v>46205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6054,7 +6044,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6097,7 +6087,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6107,14 +6097,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45211</v>
+        <v>46205</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6127,7 +6117,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6170,7 +6160,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6184,10 +6174,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46286</v>
+        <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6200,7 +6190,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6243,7 +6233,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6257,10 +6247,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46244</v>
+        <v>46259</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6272,8 +6262,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6316,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6330,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44476</v>
+        <v>44951</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6346,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.7</v>
+        <v>2.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6389,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6403,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46287</v>
+        <v>45771</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6418,13 +6413,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6467,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6481,10 +6471,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44727</v>
+        <v>44957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6497,7 +6487,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6540,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6554,10 +6544,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45282</v>
+        <v>45234</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6570,7 +6560,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6613,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6627,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45420</v>
+        <v>44967</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6642,8 +6632,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6686,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6700,10 +6695,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44636</v>
+        <v>46272</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6716,7 +6711,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6759,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6773,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45699</v>
+        <v>45744</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6788,13 +6783,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6837,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6847,14 +6837,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45387</v>
+        <v>45699</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6868,11 +6858,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6915,7 +6905,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6929,10 +6919,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45251</v>
+        <v>44636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6945,7 +6935,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6988,7 +6978,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7002,10 +6992,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45251</v>
+        <v>45628</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7017,8 +7007,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7061,7 +7056,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7075,10 +7070,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45744</v>
+        <v>45783</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7091,7 +7086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7134,7 +7129,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7148,10 +7143,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45188</v>
+        <v>46287</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7163,8 +7158,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45251</v>
+        <v>46244</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45679</v>
+        <v>46286</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45783</v>
+        <v>46132</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45644</v>
+        <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45812</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45903</v>
+        <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45197</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2084,13 +2084,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2133,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45919</v>
+        <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2163,7 +2158,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2206,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45827</v>
+        <v>45644</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2235,13 +2230,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45926</v>
+        <v>45903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2313,13 +2303,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2362,7 +2347,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2376,10 +2361,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45095</v>
+        <v>45812</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2391,8 +2376,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45000</v>
+        <v>45919</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2464,13 +2454,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2513,7 +2498,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2527,10 +2512,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45958</v>
+        <v>45827</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2542,8 +2527,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2586,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45960</v>
+        <v>45926</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2615,8 +2605,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44790</v>
+        <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2689,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45968</v>
+        <v>45000</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2761,8 +2756,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45000</v>
+        <v>44782</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2834,13 +2834,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2883,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2897,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45973</v>
+        <v>45958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2912,13 +2907,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2961,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2975,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45975</v>
+        <v>45960</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2991,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3034,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3048,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45980</v>
+        <v>45251</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3063,13 +3053,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3112,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3126,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44972</v>
+        <v>45968</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3142,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3185,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3199,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46044</v>
+        <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3215,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3258,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3272,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45216</v>
+        <v>45973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3287,8 +3272,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3331,7 +3321,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3345,10 +3335,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45446</v>
+        <v>45000</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3366,7 +3356,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3409,7 +3399,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3423,10 +3413,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45188</v>
+        <v>45975</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3439,7 +3429,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3482,7 +3472,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3492,14 +3482,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45211</v>
+        <v>45980</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3511,8 +3501,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3555,7 +3550,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3569,10 +3564,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45272</v>
+        <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3585,7 +3580,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3628,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45448</v>
+        <v>44972</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3658,7 +3653,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3701,7 +3696,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45679</v>
+        <v>45188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3731,7 +3726,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3774,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3788,10 +3783,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44812</v>
+        <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3803,8 +3798,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44972</v>
+        <v>44790</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>46132</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>46132</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46132</v>
+        <v>45095</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45716</v>
+        <v>46132</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45631</v>
+        <v>44972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45827</v>
+        <v>44967</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44516</v>
+        <v>45272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4436,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45282</v>
+        <v>45716</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45181</v>
+        <v>45827</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4538,8 +4538,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4582,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4596,10 +4601,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44782</v>
+        <v>45471</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4612,7 +4617,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4655,7 +4660,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4669,10 +4674,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46153</v>
+        <v>44516</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4684,13 +4689,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4733,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44727</v>
+        <v>46153</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4762,8 +4762,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>8.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4806,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4820,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44476</v>
+        <v>45628</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4835,8 +4840,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4896,7 +4906,7 @@
         <v>46161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4974,7 +4984,7 @@
         <v>46162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5052,7 +5062,7 @@
         <v>46162</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5113,7 +5123,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5137,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44972</v>
+        <v>45181</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5143,7 +5153,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5186,7 +5196,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5200,10 +5210,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45588</v>
+        <v>45448</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5216,7 +5226,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5259,7 +5269,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5273,10 +5283,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45420</v>
+        <v>45588</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5289,7 +5299,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5332,7 +5342,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5346,10 +5356,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45188</v>
+        <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5362,7 +5372,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5405,7 +5415,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5415,14 +5425,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44972</v>
+        <v>45211</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5435,7 +5445,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5478,7 +5488,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5492,10 +5502,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45471</v>
+        <v>46204</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5507,8 +5517,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5551,7 +5566,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5565,10 +5580,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5580,13 +5595,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5629,7 +5639,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5643,10 +5653,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5658,13 +5668,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5707,7 +5712,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5721,10 +5726,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45251</v>
+        <v>44476</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5737,7 +5742,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>6.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5780,7 +5785,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5794,10 +5799,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5815,7 +5820,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5858,7 +5863,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5868,14 +5873,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45387</v>
+        <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5898,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5953,7 +5958,7 @@
         <v>46205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6014,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6028,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46205</v>
+        <v>44727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6044,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6087,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6101,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46205</v>
+        <v>45282</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6117,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6160,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6174,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45251</v>
+        <v>46259</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6189,8 +6194,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6233,7 +6243,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6247,10 +6257,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46259</v>
+        <v>46272</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6262,13 +6272,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6316,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6330,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44951</v>
+        <v>45420</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6346,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45771</v>
+        <v>44636</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6419,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6476,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44957</v>
+        <v>45699</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6486,8 +6491,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6530,7 +6540,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6540,14 +6550,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45234</v>
+        <v>45387</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6559,8 +6569,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6618,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6617,10 +6632,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44967</v>
+        <v>45251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6632,13 +6647,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6691,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6695,10 +6705,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46272</v>
+        <v>45251</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6711,7 +6721,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6771,7 +6781,7 @@
         <v>45744</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6827,7 +6837,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6851,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45699</v>
+        <v>45188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6856,13 +6866,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6905,7 +6910,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6919,10 +6924,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44636</v>
+        <v>46286</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6935,7 +6940,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6978,7 +6983,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6992,10 +6997,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45628</v>
+        <v>46244</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7007,13 +7012,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45783</v>
+        <v>45251</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7146,7 +7146,7 @@
         <v>46287</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46244</v>
+        <v>45679</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46286</v>
+        <v>45783</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
         <v>46132</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13578-2022</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 13578-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45771</v>
+        <v>45181</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>44790</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44812</v>
+        <v>45000</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,8 +1860,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>44951</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1931,11 +1936,6 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44951</v>
+        <v>44782</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>45771</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45234</v>
+        <v>44727</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45644</v>
+        <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45903</v>
+        <v>44957</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45812</v>
+        <v>45234</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2376,13 +2376,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2425,7 +2420,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,10 +2434,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45919</v>
+        <v>44476</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2455,7 +2450,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2493,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2507,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45827</v>
+        <v>44967</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2528,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2571,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2585,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45926</v>
+        <v>45216</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2605,13 +2600,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2644,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2658,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46044</v>
+        <v>45744</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2674,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2717,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2731,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45000</v>
+        <v>45699</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2758,11 +2748,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2795,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2809,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44782</v>
+        <v>44636</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2878,7 +2868,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2882,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45958</v>
+        <v>45628</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2907,8 +2897,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45960</v>
+        <v>44972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45251</v>
+        <v>45446</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3053,8 +3048,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45968</v>
+        <v>45188</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3180,14 +3180,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44972</v>
+        <v>45211</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45973</v>
+        <v>45783</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3272,13 +3272,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45000</v>
+        <v>45272</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3350,13 +3345,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3399,7 +3389,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3413,10 +3403,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45975</v>
+        <v>45420</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3429,7 +3419,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3472,7 +3462,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3486,10 +3476,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45980</v>
+        <v>45448</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3501,13 +3491,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3550,7 +3535,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3564,10 +3549,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44972</v>
+        <v>45188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3580,7 +3565,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3623,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3637,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44972</v>
+        <v>45679</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3653,7 +3638,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3696,7 +3681,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3710,10 +3695,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45188</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3726,7 +3711,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3754,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3768,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45197</v>
+        <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3798,13 +3783,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3847,7 +3827,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3861,10 +3841,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44790</v>
+        <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3877,7 +3857,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3920,7 +3900,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3934,10 +3914,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46132</v>
+        <v>45197</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3949,8 +3929,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3993,7 +3978,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4007,10 +3992,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46132</v>
+        <v>44812</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4023,7 +4008,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4066,7 +4051,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4065,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45095</v>
+        <v>45471</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4096,7 +4081,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4124,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4138,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46132</v>
+        <v>44972</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4169,7 +4154,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4212,7 +4197,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4226,10 +4211,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44972</v>
+        <v>45644</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4242,7 +4227,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4270,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,10 +4284,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44967</v>
+        <v>45812</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4316,11 +4301,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4348,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4377,10 +4362,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45272</v>
+        <v>45251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4393,7 +4378,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4421,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4446,14 +4431,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45716</v>
+        <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4465,8 +4450,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4509,7 +4499,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4526,7 +4516,7 @@
         <v>45827</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4544,7 +4534,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4577,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4601,10 +4591,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45471</v>
+        <v>45095</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4617,7 +4607,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4660,7 +4650,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4674,10 +4664,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44516</v>
+        <v>45631</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4690,7 +4680,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4733,7 +4723,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4737,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46153</v>
+        <v>45251</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4762,13 +4752,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4796,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4810,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45628</v>
+        <v>45282</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4840,13 +4825,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4889,7 +4869,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4903,10 +4883,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46161</v>
+        <v>45000</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4920,11 +4900,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4947,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4961,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46162</v>
+        <v>45958</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4996,13 +4976,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>7.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5020,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5034,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46162</v>
+        <v>45960</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5074,13 +5049,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5123,7 +5093,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5137,10 +5107,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45181</v>
+        <v>45903</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5153,7 +5123,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5196,7 +5166,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5210,10 +5180,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45448</v>
+        <v>45919</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5226,7 +5196,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5269,7 +5239,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5283,10 +5253,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45588</v>
+        <v>45968</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5299,7 +5269,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5342,7 +5312,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5356,10 +5326,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45631</v>
+        <v>45973</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5371,8 +5341,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5415,7 +5390,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5425,14 +5400,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45211</v>
+        <v>45926</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5444,8 +5419,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5488,7 +5468,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5502,10 +5482,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46204</v>
+        <v>45975</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5517,13 +5497,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5566,7 +5541,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5580,10 +5555,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46205</v>
+        <v>45980</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5595,8 +5570,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5639,7 +5619,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5653,10 +5633,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46205</v>
+        <v>46044</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5669,7 +5649,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5712,7 +5692,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5726,10 +5706,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44476</v>
+        <v>46132</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5742,7 +5722,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5785,7 +5765,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5799,10 +5779,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46204</v>
+        <v>46132</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5814,13 +5794,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>9.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5863,7 +5838,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5877,10 +5852,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5892,13 +5867,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5941,7 +5911,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5955,10 +5925,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46205</v>
+        <v>45716</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5970,13 +5940,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +5984,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +5998,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44727</v>
+        <v>45827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6048,8 +6013,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6062,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6076,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45282</v>
+        <v>44516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6122,7 +6092,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6135,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6149,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46259</v>
+        <v>46153</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6200,7 +6170,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6243,7 +6213,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6257,10 +6227,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46272</v>
+        <v>46161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6272,8 +6242,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6316,7 +6291,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6330,10 +6305,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45420</v>
+        <v>46162</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6345,8 +6320,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6389,7 +6369,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6403,10 +6383,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44636</v>
+        <v>46162</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6418,8 +6398,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6447,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6476,10 +6461,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45699</v>
+        <v>45588</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6491,13 +6476,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6540,7 +6520,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6550,14 +6530,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45387</v>
+        <v>46204</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6575,7 +6555,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6618,7 +6598,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6632,10 +6612,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45251</v>
+        <v>46204</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6647,8 +6627,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6691,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6705,10 +6690,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45251</v>
+        <v>46205</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6720,8 +6705,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6764,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6778,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45744</v>
+        <v>46205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6793,8 +6783,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6837,7 +6832,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6851,10 +6846,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45188</v>
+        <v>46205</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6867,7 +6862,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6910,7 +6905,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6924,10 +6919,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46286</v>
+        <v>46205</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6940,7 +6935,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6983,7 +6978,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6997,10 +6992,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46244</v>
+        <v>46259</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7012,8 +7007,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45251</v>
+        <v>46272</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7146,7 +7146,7 @@
         <v>46287</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45679</v>
+        <v>46244</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45783</v>
+        <v>46286</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
         <v>46132</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 13578-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13578-2022</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45181</v>
+        <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44790</v>
+        <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45000</v>
+        <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,13 +1860,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1909,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44951</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1936,6 +1931,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44782</v>
+        <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45771</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44727</v>
+        <v>46044</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44972</v>
+        <v>45234</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44957</v>
+        <v>45903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45234</v>
+        <v>45919</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2420,7 +2420,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44476</v>
+        <v>45926</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2449,8 +2449,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2493,7 +2498,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2507,10 +2512,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44967</v>
+        <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2522,13 +2527,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45216</v>
+        <v>45958</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45744</v>
+        <v>45812</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2673,8 +2673,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2717,7 +2722,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2731,10 +2736,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45699</v>
+        <v>45000</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2748,11 +2753,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2795,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2809,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44636</v>
+        <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2825,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2868,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45628</v>
+        <v>45968</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2897,13 +2902,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44972</v>
+        <v>44782</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45446</v>
+        <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45188</v>
+        <v>45251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3180,14 +3180,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45211</v>
+        <v>45975</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45783</v>
+        <v>45980</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3272,8 +3272,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3321,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3335,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45272</v>
+        <v>46132</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3346,7 +3351,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3389,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3403,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45420</v>
+        <v>46132</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3419,7 +3424,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3462,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3476,10 +3481,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45448</v>
+        <v>46132</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3492,7 +3497,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3535,7 +3540,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45188</v>
+        <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3565,7 +3570,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3613,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3627,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45679</v>
+        <v>45000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3637,8 +3642,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3681,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3695,10 +3705,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3711,7 +3721,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3754,7 +3764,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3768,10 +3778,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45251</v>
+        <v>44972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3784,7 +3794,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3827,7 +3837,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3841,10 +3851,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44972</v>
+        <v>45716</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3857,7 +3867,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3900,7 +3910,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3914,10 +3924,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45197</v>
+        <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3929,13 +3939,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3978,7 +3983,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3992,10 +3997,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44812</v>
+        <v>45827</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4007,8 +4012,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4051,7 +4061,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4065,10 +4075,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45471</v>
+        <v>45197</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4080,8 +4090,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4124,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4138,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44972</v>
+        <v>45827</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4153,8 +4168,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4197,7 +4217,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4211,10 +4231,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45644</v>
+        <v>44516</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4227,7 +4247,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4270,7 +4290,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4284,10 +4304,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45812</v>
+        <v>44790</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4299,13 +4319,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4348,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4362,10 +4377,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45251</v>
+        <v>45095</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4378,7 +4393,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4421,7 +4436,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4431,14 +4446,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45387</v>
+        <v>46153</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4456,7 +4471,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4499,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4513,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45827</v>
+        <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4528,13 +4543,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4577,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4591,10 +4601,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45095</v>
+        <v>46161</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4606,8 +4616,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4650,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4664,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45631</v>
+        <v>46162</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4679,8 +4694,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4723,7 +4743,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4737,10 +4757,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45251</v>
+        <v>46162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4752,8 +4772,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4796,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4810,10 +4835,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45282</v>
+        <v>44967</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4825,8 +4850,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4869,7 +4899,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4883,10 +4913,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45000</v>
+        <v>45272</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4898,13 +4928,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4947,7 +4972,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4961,10 +4986,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45958</v>
+        <v>45471</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4977,7 +5002,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5020,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5034,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45960</v>
+        <v>45588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5050,7 +5075,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5093,7 +5118,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5107,10 +5132,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45903</v>
+        <v>45628</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5122,8 +5147,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5166,7 +5196,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5180,10 +5210,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45919</v>
+        <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5195,8 +5225,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5239,7 +5274,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5253,10 +5288,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45968</v>
+        <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5269,7 +5304,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5312,7 +5347,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5326,10 +5361,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45973</v>
+        <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5341,13 +5376,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5390,7 +5420,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5404,10 +5434,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45926</v>
+        <v>46204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5425,7 +5455,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5468,7 +5498,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5482,10 +5512,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45975</v>
+        <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5497,8 +5527,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5541,7 +5576,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5555,10 +5590,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45980</v>
+        <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5572,11 +5607,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5619,7 +5654,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5633,10 +5668,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46044</v>
+        <v>45181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5649,7 +5684,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5692,7 +5727,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5706,10 +5741,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46132</v>
+        <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5721,8 +5756,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5765,7 +5805,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5779,10 +5819,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46132</v>
+        <v>45448</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5795,7 +5835,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5838,7 +5878,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5852,10 +5892,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46132</v>
+        <v>46272</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5868,7 +5908,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5911,7 +5951,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5925,10 +5965,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45716</v>
+        <v>45631</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5941,7 +5981,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5984,7 +6024,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5994,14 +6034,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45827</v>
+        <v>45211</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6013,13 +6053,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6062,7 +6097,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6076,10 +6111,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44516</v>
+        <v>44476</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6092,7 +6127,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6135,7 +6170,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6149,10 +6184,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46153</v>
+        <v>44727</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6164,13 +6199,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>8.5</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6213,7 +6243,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6227,10 +6257,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46161</v>
+        <v>45282</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6242,13 +6272,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6291,7 +6316,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6305,10 +6330,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46162</v>
+        <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6320,13 +6345,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6369,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6383,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46162</v>
+        <v>46244</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6398,13 +6418,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6447,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6461,10 +6476,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45588</v>
+        <v>46287</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6476,8 +6491,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6520,7 +6540,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6534,10 +6554,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46204</v>
+        <v>45420</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6549,13 +6569,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6598,7 +6613,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6612,10 +6627,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46204</v>
+        <v>44636</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6627,13 +6642,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6676,7 +6686,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6690,10 +6700,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46205</v>
+        <v>45699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6707,11 +6717,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6764,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6778,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6783,13 +6793,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6832,7 +6837,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6842,14 +6847,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46205</v>
+        <v>45387</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6861,8 +6866,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6905,7 +6915,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6919,10 +6929,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46205</v>
+        <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6935,7 +6945,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6978,7 +6988,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6992,10 +7002,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46259</v>
+        <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7007,13 +7017,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7056,7 +7061,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7070,10 +7075,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46272</v>
+        <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7086,7 +7091,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7129,7 +7134,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7143,10 +7148,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46287</v>
+        <v>45188</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7158,13 +7163,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46244</v>
+        <v>45251</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46286</v>
+        <v>45679</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46132</v>
+        <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45771</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44812</v>
+        <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,8 +1860,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>45903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1933,13 +1938,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44951</v>
+        <v>46044</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>45919</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46044</v>
+        <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2157,8 +2157,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2206,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45234</v>
+        <v>45095</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2231,7 +2236,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2279,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2288,10 +2293,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45903</v>
+        <v>45000</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2303,8 +2308,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2347,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2361,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45919</v>
+        <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2377,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2420,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2434,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45926</v>
+        <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2451,11 +2461,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45644</v>
+        <v>45958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2528,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2571,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2585,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45958</v>
+        <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2601,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.3</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2644,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2658,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45812</v>
+        <v>45960</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2673,13 +2683,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2722,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2739,7 +2744,7 @@
         <v>45000</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45960</v>
+        <v>45968</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45968</v>
+        <v>45973</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2902,8 +2907,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2956,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2970,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44782</v>
+        <v>44972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2986,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3029,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3043,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3048,13 +3058,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3102,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3116,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45251</v>
+        <v>45980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3126,8 +3131,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3180,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3194,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45975</v>
+        <v>45216</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3210,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3253,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3267,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45980</v>
+        <v>45827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3274,11 +3284,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3338,7 +3348,7 @@
         <v>46132</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3411,7 +3421,7 @@
         <v>46132</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3484,7 +3494,7 @@
         <v>46132</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3540,7 +3550,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,10 +3564,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44972</v>
+        <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3570,7 +3580,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3613,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3627,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45000</v>
+        <v>45446</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3648,7 +3658,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3691,7 +3701,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44972</v>
+        <v>45188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3764,7 +3774,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3774,14 +3784,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44972</v>
+        <v>45211</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3794,7 +3804,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3837,7 +3847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45716</v>
+        <v>45827</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3866,8 +3876,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3910,7 +3925,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3924,10 +3939,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45188</v>
+        <v>45272</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3940,7 +3955,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3983,7 +3998,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3997,10 +4012,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45827</v>
+        <v>45448</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4012,13 +4027,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4061,7 +4071,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4075,10 +4085,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45197</v>
+        <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4090,13 +4100,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4144,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4158,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45827</v>
+        <v>45679</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4168,13 +4173,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4217,7 +4217,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44516</v>
+        <v>44812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4290,7 +4290,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44790</v>
+        <v>44972</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45095</v>
+        <v>46153</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4392,8 +4392,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4441,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4450,10 +4455,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46153</v>
+        <v>45631</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4465,13 +4470,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44972</v>
+        <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4543,8 +4543,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4622,7 +4627,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4665,7 +4670,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4682,7 +4687,7 @@
         <v>46162</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4700,7 +4705,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4743,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4757,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46162</v>
+        <v>45282</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4772,13 +4777,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44967</v>
+        <v>45181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4848,11 +4848,6 @@
       <c r="G57" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -4899,7 +4894,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4913,10 +4908,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45272</v>
+        <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4929,7 +4924,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4972,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4986,10 +4981,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45471</v>
+        <v>44782</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5002,7 +4997,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45588</v>
+        <v>44727</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5075,7 +5070,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5118,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45628</v>
+        <v>44476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5147,13 +5142,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5196,7 +5186,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5213,7 +5203,7 @@
         <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5221,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5274,7 +5264,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5288,10 +5278,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5301,6 +5291,11 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5347,7 +5342,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5364,7 +5359,7 @@
         <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5376,8 +5371,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>9.4</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5515,7 +5515,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5527,13 +5527,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5576,7 +5571,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5593,7 +5588,7 @@
         <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5605,13 +5600,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5654,7 +5644,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5668,10 +5658,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45181</v>
+        <v>46259</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5683,8 +5673,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5727,7 +5722,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5741,10 +5736,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46259</v>
+        <v>44972</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5756,13 +5751,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5805,7 +5795,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5819,10 +5809,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45448</v>
+        <v>46272</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5835,7 +5825,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5878,7 +5868,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5892,10 +5882,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46272</v>
+        <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5908,7 +5898,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5951,7 +5941,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5965,10 +5955,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45631</v>
+        <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5981,7 +5971,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6024,7 +6014,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6034,14 +6024,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45211</v>
+        <v>46287</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6053,8 +6043,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6097,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6111,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44476</v>
+        <v>46244</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6127,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6170,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6184,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44727</v>
+        <v>46286</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6200,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6243,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6257,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45282</v>
+        <v>44972</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6273,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6316,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6330,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46286</v>
+        <v>45471</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6346,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6389,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6403,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46244</v>
+        <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6419,7 +6414,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6472,14 +6467,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46287</v>
+        <v>45387</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6497,7 +6492,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6540,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6554,10 +6549,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45420</v>
+        <v>46132</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6570,7 +6565,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6613,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6627,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44636</v>
+        <v>45251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6643,7 +6638,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6686,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6700,10 +6695,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45699</v>
+        <v>44951</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6715,13 +6710,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6764,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6778,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46132</v>
+        <v>45771</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6794,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6837,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6847,14 +6837,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45387</v>
+        <v>44957</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6866,13 +6856,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6915,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6929,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45251</v>
+        <v>45234</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6945,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6988,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7002,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45251</v>
+        <v>44967</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7017,8 +7002,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7078,7 +7068,7 @@
         <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7134,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7148,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45188</v>
+        <v>45699</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7163,8 +7153,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7207,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7221,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45251</v>
+        <v>44636</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7237,7 +7232,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45679</v>
+        <v>45628</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7309,8 +7304,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
         <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>45903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>46044</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45919</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45095</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45000</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45960</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45000</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45968</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45973</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>44972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45975</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45216</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>46132</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>46132</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46132</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>45446</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>45188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45211</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>45827</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45272</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45448</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45679</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>44812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44972</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>46153</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>45631</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>46162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>46162</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45282</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>44782</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>44727</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>46204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>46259</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44972</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>46272</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>46287</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>46244</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>46286</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44972</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45471</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45387</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>46132</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44951</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45771</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44957</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45234</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44967</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45699</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>44636</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45628</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>45903</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>46044</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45919</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45095</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45000</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45960</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45000</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45968</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45973</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>44972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45975</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45216</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45827</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>46132</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>46132</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46132</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>45446</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>45188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45211</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>45827</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45272</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45448</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45679</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>44812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>44972</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>46153</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>45631</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46161</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>46162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>46162</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>45282</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>45181</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>44782</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>44727</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44476</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>46204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>46259</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44972</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>46272</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>46287</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>46244</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>46286</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44972</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45471</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45387</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>46132</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44951</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>45771</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44957</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>45234</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44967</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45699</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>44636</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45628</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45197</v>
+        <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,13 +1860,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1909,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45903</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1938,8 +1933,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46044</v>
+        <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45919</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45926</v>
+        <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2157,13 +2157,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2206,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45095</v>
+        <v>45644</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2236,7 +2231,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2279,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45000</v>
+        <v>45812</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2310,11 +2305,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2352,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2366,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45644</v>
+        <v>46044</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2382,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45812</v>
+        <v>45827</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2461,11 +2456,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45958</v>
+        <v>45903</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2533,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44790</v>
+        <v>45000</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2610,8 +2605,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45960</v>
+        <v>45919</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45000</v>
+        <v>44782</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2756,13 +2756,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45968</v>
+        <v>45926</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2834,8 +2829,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45973</v>
+        <v>45251</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2907,13 +2907,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2956,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2973,7 +2968,7 @@
         <v>44972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2986,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3029,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3043,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45975</v>
+        <v>45000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3058,8 +3053,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45980</v>
+        <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3131,13 +3131,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3180,7 +3175,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45216</v>
+        <v>44972</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3210,7 +3205,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3253,7 +3248,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3267,10 +3262,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45827</v>
+        <v>45958</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3282,13 +3277,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3331,7 +3321,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3345,10 +3335,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46132</v>
+        <v>45960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3361,7 +3351,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3404,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3418,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46132</v>
+        <v>45968</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3434,7 +3424,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3477,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3491,10 +3481,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46132</v>
+        <v>45188</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3507,7 +3497,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3550,7 +3540,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3564,10 +3554,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45716</v>
+        <v>45973</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3579,8 +3569,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3623,7 +3618,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3637,10 +3632,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45446</v>
+        <v>45197</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3658,7 +3653,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3701,7 +3696,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45188</v>
+        <v>45975</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3731,7 +3726,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3774,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3784,14 +3779,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45211</v>
+        <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3803,8 +3798,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45827</v>
+        <v>46132</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3876,13 +3876,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3925,7 +3920,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3939,10 +3934,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45272</v>
+        <v>44790</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3955,7 +3950,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3998,7 +3993,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4012,10 +4007,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45448</v>
+        <v>46132</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4028,7 +4023,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4071,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4085,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44516</v>
+        <v>46132</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4101,7 +4096,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4144,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4158,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45679</v>
+        <v>45095</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4174,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4217,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4231,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44812</v>
+        <v>44972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4247,7 +4242,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4290,7 +4285,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4304,10 +4299,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44972</v>
+        <v>44967</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4319,8 +4314,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46153</v>
+        <v>45716</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4392,13 +4392,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>8.5</v>
+        <v>4.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4441,7 +4436,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4455,10 +4450,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45631</v>
+        <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4471,7 +4466,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4514,7 +4509,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4523,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46161</v>
+        <v>45827</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4545,11 +4540,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4606,10 +4601,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46162</v>
+        <v>44516</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4621,13 +4616,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4670,7 +4660,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4684,10 +4674,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46162</v>
+        <v>45471</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4699,13 +4689,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4748,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4762,10 +4747,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45282</v>
+        <v>46153</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4777,8 +4762,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4821,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4835,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45181</v>
+        <v>46161</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4850,8 +4840,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45588</v>
+        <v>46162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4923,8 +4918,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44782</v>
+        <v>46162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4996,8 +4996,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5040,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44727</v>
+        <v>45628</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5069,8 +5074,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5123,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5137,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44476</v>
+        <v>45588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5143,7 +5153,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5186,7 +5196,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5200,10 +5210,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46204</v>
+        <v>45181</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5215,13 +5225,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>9.4</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5264,7 +5269,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46204</v>
+        <v>45448</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5293,13 +5298,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5342,7 +5342,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46205</v>
+        <v>45631</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5449,13 +5449,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5515,7 +5510,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5588,7 +5583,7 @@
         <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5644,7 +5639,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5658,10 +5653,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46259</v>
+        <v>46204</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5679,7 +5674,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>9.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5722,7 +5717,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5736,10 +5731,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44972</v>
+        <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5751,8 +5746,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5795,7 +5795,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46272</v>
+        <v>46205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5824,8 +5824,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5868,7 +5873,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5878,14 +5883,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45420</v>
+        <v>45211</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5898,7 +5903,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5941,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5955,10 +5960,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45188</v>
+        <v>46259</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5970,8 +5975,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6014,7 +6024,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6028,10 +6038,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46287</v>
+        <v>44476</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6043,13 +6053,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6097,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6111,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46244</v>
+        <v>44727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6122,7 +6127,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6170,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6184,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6200,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6243,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6257,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44972</v>
+        <v>45282</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6273,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6316,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6330,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45471</v>
+        <v>45420</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6346,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45251</v>
+        <v>44636</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6419,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6467,14 +6472,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45387</v>
+        <v>46286</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6486,13 +6491,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46132</v>
+        <v>46244</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45251</v>
+        <v>45699</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6637,8 +6637,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6686,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6695,10 +6700,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44951</v>
+        <v>46287</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6710,8 +6715,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6764,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6764,14 +6774,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45771</v>
+        <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6783,8 +6793,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6842,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6856,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44957</v>
+        <v>45251</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6900,7 +6915,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6929,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45234</v>
+        <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6945,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6988,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +7002,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44967</v>
+        <v>45744</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7002,13 +7017,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7061,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7075,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45744</v>
+        <v>45188</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7091,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7134,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7148,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45699</v>
+        <v>45251</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,13 +7163,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7207,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7221,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44636</v>
+        <v>45679</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7232,7 +7237,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45628</v>
+        <v>46132</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7304,13 +7309,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
         <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE98"/>
+  <dimension ref="A1:AE99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45771</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44812</v>
+        <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,8 +1860,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>45095</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1933,13 +1938,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44951</v>
+        <v>45644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>46044</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45234</v>
+        <v>45812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2157,8 +2157,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2206,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45644</v>
+        <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2230,8 +2235,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2288,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45812</v>
+        <v>45903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2303,13 +2313,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2352,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2366,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46044</v>
+        <v>45919</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2382,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2442,7 +2447,7 @@
         <v>45827</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2503,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45903</v>
+        <v>44790</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2593,7 +2598,7 @@
         <v>45000</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45919</v>
+        <v>45926</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2683,8 +2688,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2737,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2751,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44782</v>
+        <v>44972</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2767,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2810,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2824,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45926</v>
+        <v>45958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2829,13 +2839,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2883,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2897,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45251</v>
+        <v>45960</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2913,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2956,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2970,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44972</v>
+        <v>45216</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2986,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3029,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3043,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45000</v>
+        <v>46132</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3053,13 +3058,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44972</v>
+        <v>46132</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44972</v>
+        <v>46132</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45958</v>
+        <v>45968</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45960</v>
+        <v>45973</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3350,8 +3350,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45968</v>
+        <v>45975</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3467,7 +3472,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45188</v>
+        <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3497,7 +3502,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3540,7 +3545,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45973</v>
+        <v>45980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3571,11 +3576,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3618,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3632,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45197</v>
+        <v>45827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3653,7 +3658,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3696,7 +3701,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45975</v>
+        <v>44516</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3726,7 +3731,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3774,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3788,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45980</v>
+        <v>46153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3800,11 +3805,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3847,7 +3852,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3861,10 +3866,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3876,8 +3881,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3920,7 +3930,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3934,10 +3944,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44790</v>
+        <v>46162</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3949,8 +3959,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3993,7 +4008,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4007,10 +4022,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46132</v>
+        <v>46162</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4022,8 +4037,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4066,7 +4086,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4100,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46132</v>
+        <v>45446</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4095,8 +4115,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4164,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4178,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45095</v>
+        <v>45188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4212,7 +4237,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4222,14 +4247,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44972</v>
+        <v>45211</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4242,7 +4267,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4310,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,10 +4324,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44967</v>
+        <v>45588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4314,13 +4339,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4383,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4377,10 +4397,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45716</v>
+        <v>45272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4393,7 +4413,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4456,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4450,10 +4470,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45272</v>
+        <v>45448</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4466,7 +4486,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4509,7 +4529,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4523,10 +4543,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45827</v>
+        <v>45679</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4538,13 +4558,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4602,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4601,10 +4616,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44516</v>
+        <v>44812</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4617,7 +4632,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4660,7 +4675,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4674,10 +4689,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45471</v>
+        <v>44972</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4690,7 +4705,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4733,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46153</v>
+        <v>46204</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4768,7 +4783,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4826,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4840,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46161</v>
+        <v>46204</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4842,11 +4857,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4889,7 +4904,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4903,10 +4918,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46162</v>
+        <v>46205</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4920,11 +4935,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4982,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4996,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46162</v>
+        <v>46205</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4998,11 +5013,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5060,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5074,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45628</v>
+        <v>46205</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5074,13 +5089,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5123,7 +5133,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5137,10 +5147,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45588</v>
+        <v>46205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5196,7 +5206,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5210,10 +5220,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45181</v>
+        <v>45631</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5226,7 +5236,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5269,7 +5279,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5283,10 +5293,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45448</v>
+        <v>45282</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5299,7 +5309,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5342,7 +5352,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5356,10 +5366,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46204</v>
+        <v>45181</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5371,13 +5381,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5420,7 +5425,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5434,10 +5439,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45631</v>
+        <v>44782</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5455,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5493,7 +5498,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5507,10 +5512,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46205</v>
+        <v>44727</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5523,7 +5528,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5566,7 +5571,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 55664-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5580,10 +5585,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46205</v>
+        <v>44476</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5601,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>6.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5639,7 +5644,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5653,10 +5658,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46204</v>
+        <v>46272</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5668,13 +5673,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>9.4</v>
+        <v>3.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46205</v>
+        <v>46287</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5795,7 +5795,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5824,13 +5824,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5873,7 +5868,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5883,14 +5878,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45211</v>
+        <v>46286</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5903,7 +5898,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5941,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5960,10 +5955,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46259</v>
+        <v>44972</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5975,13 +5970,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6024,7 +6014,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6038,10 +6028,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44476</v>
+        <v>45420</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6054,7 +6044,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6097,7 +6087,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6111,10 +6101,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44727</v>
+        <v>45188</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6127,7 +6117,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6170,7 +6160,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6184,10 +6174,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46272</v>
+        <v>46132</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6200,7 +6190,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6243,7 +6233,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6257,10 +6247,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45282</v>
+        <v>44972</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6273,7 +6263,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6316,7 +6306,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6330,10 +6320,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45420</v>
+        <v>45471</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6346,7 +6336,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6389,7 +6379,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6403,10 +6393,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44636</v>
+        <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6419,7 +6409,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6452,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6472,14 +6462,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46286</v>
+        <v>45387</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6491,8 +6481,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6549,10 +6544,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46244</v>
+        <v>46301</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6565,7 +6560,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45699</v>
+        <v>45251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6637,13 +6632,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6686,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6700,10 +6690,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46287</v>
+        <v>46259</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6764,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6774,14 +6764,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45387</v>
+        <v>44951</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6793,13 +6783,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6842,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6856,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6872,7 +6857,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6915,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6929,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45251</v>
+        <v>44957</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6988,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7002,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45744</v>
+        <v>45234</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7018,7 +7003,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7061,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7075,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45188</v>
+        <v>44967</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7090,8 +7075,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7134,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7148,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45251</v>
+        <v>45744</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7164,7 +7154,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7207,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7221,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45679</v>
+        <v>45699</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7236,8 +7226,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46132</v>
+        <v>44636</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7353,7 +7348,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7362,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45783</v>
+        <v>45628</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7382,8 +7377,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,24 +7426,24 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45783</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7455,13 +7455,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7499,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7513,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7534,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7577,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7599,7 +7594,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7612,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7655,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7669,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7690,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>52.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7755,7 +7750,7 @@
         <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7833,7 +7828,7 @@
         <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7891,83 +7886,161 @@
       </c>
       <c r="V97" s="2" t="inlineStr"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
+          <t>S 923-2022</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>44606</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>S 4416-2023</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D98" s="1" t="n">
+      <c r="D99" s="1" t="n">
         <v>45266</v>
       </c>
-      <c r="E98" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="E99" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>Bergvik skog väst AB</t>
         </is>
       </c>
-      <c r="I98" t="n">
+      <c r="I99" t="n">
         <v>40</v>
       </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="S98" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" t="n">
-        <v>0</v>
-      </c>
-      <c r="V98" s="2" t="inlineStr"/>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE99"/>
+  <dimension ref="A1:AE98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 18303-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44648</v>
+        <v>44685</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1563,8 +1563,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18303-2022</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44685</v>
+        <v>45188</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1636,13 +1641,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45197</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1714,8 +1714,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1763,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1777,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1793,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1836,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1850,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45197</v>
+        <v>44648</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,13 +1865,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45095</v>
+        <v>45679</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45644</v>
+        <v>44790</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46044</v>
+        <v>45783</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45812</v>
+        <v>45216</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2155,11 +2155,6 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2206,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45000</v>
+        <v>45095</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2235,13 +2230,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45903</v>
+        <v>44812</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2304,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2347,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2361,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45919</v>
+        <v>45446</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2386,8 +2376,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45827</v>
+        <v>44972</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2459,13 +2454,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2498,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2512,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44790</v>
+        <v>45903</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2528,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2571,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2585,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45000</v>
+        <v>44951</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2610,13 +2600,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2644,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2658,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45926</v>
+        <v>45644</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2688,13 +2673,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2737,7 +2717,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2751,10 +2731,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44972</v>
+        <v>44957</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2767,7 +2747,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2810,7 +2790,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2824,10 +2804,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45958</v>
+        <v>45919</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2840,7 +2820,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2883,7 +2863,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2897,10 +2877,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45960</v>
+        <v>45812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2912,8 +2892,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2956,7 +2941,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2970,10 +2955,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45216</v>
+        <v>44967</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2985,8 +2970,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3029,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3043,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46132</v>
+        <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3059,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3102,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3116,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46132</v>
+        <v>45926</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3131,8 +3121,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3175,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3189,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46132</v>
+        <v>45234</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3205,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3248,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3262,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45968</v>
+        <v>45471</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3278,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45973</v>
+        <v>45827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3356,7 +3351,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3399,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3413,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45975</v>
+        <v>45958</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3429,7 +3424,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3472,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45716</v>
+        <v>45960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3502,7 +3497,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3545,7 +3540,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3559,10 +3554,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45980</v>
+        <v>45968</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3574,13 +3569,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3623,7 +3613,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3637,10 +3627,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45827</v>
+        <v>45973</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3658,7 +3648,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3701,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3715,10 +3705,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44516</v>
+        <v>45628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3730,8 +3720,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3774,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3788,10 +3783,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46153</v>
+        <v>45975</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3803,13 +3798,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3852,7 +3842,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3866,10 +3856,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46161</v>
+        <v>45000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3883,11 +3873,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3930,7 +3920,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3944,10 +3934,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46162</v>
+        <v>45716</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3959,13 +3949,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4008,7 +3993,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4022,10 +4007,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46162</v>
+        <v>45980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4043,7 +4028,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4086,7 +4071,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4100,10 +4085,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45446</v>
+        <v>45827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4121,7 +4106,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4164,7 +4149,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4178,10 +4163,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45188</v>
+        <v>44516</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4194,7 +4179,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4237,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4247,14 +4232,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45211</v>
+        <v>44782</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4267,7 +4252,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4310,7 +4295,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4324,10 +4309,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45588</v>
+        <v>46153</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4339,8 +4324,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4383,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4397,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45272</v>
+        <v>45251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4456,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4470,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45448</v>
+        <v>45181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4486,7 +4476,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4529,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4543,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45679</v>
+        <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4559,7 +4549,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4602,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4616,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44812</v>
+        <v>46161</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4631,8 +4621,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4675,7 +4670,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44972</v>
+        <v>45000</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4704,8 +4699,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46204</v>
+        <v>46162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4779,11 +4779,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>9.4</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46204</v>
+        <v>44972</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4855,13 +4855,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4904,7 +4899,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4918,10 +4913,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46205</v>
+        <v>44972</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4933,13 +4928,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4982,7 +4972,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4996,10 +4986,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46205</v>
+        <v>46162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5013,11 +5003,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5060,7 +5050,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5074,10 +5064,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46205</v>
+        <v>45448</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5090,7 +5080,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5133,7 +5123,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5147,10 +5137,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46205</v>
+        <v>45631</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5163,7 +5153,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5206,7 +5196,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5220,10 +5210,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45631</v>
+        <v>45588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5236,7 +5226,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5279,7 +5269,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5293,10 +5283,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45282</v>
+        <v>46044</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5309,7 +5299,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5352,7 +5342,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5362,14 +5352,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45181</v>
+        <v>45211</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5382,7 +5372,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5425,7 +5415,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5439,10 +5429,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44782</v>
+        <v>46204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5454,8 +5444,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5515,7 +5510,7 @@
         <v>44727</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5571,7 +5566,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55664-2021</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5585,10 +5580,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44476</v>
+        <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5596,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5644,7 +5639,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5658,10 +5653,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46272</v>
+        <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5669,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5717,7 +5712,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5731,10 +5726,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46287</v>
+        <v>45282</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5746,13 +5741,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5795,7 +5785,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5809,10 +5799,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46244</v>
+        <v>46204</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5824,8 +5814,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5868,7 +5863,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5882,10 +5877,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46286</v>
+        <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5897,8 +5892,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5941,7 +5941,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44972</v>
+        <v>46205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5970,8 +5970,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6014,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6028,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45420</v>
+        <v>46132</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6044,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6087,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6101,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45188</v>
+        <v>46132</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6117,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6160,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6177,7 +6182,7 @@
         <v>46132</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6190,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6233,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6247,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44972</v>
+        <v>45420</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6263,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6306,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6320,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45471</v>
+        <v>44636</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6336,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6379,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6393,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45251</v>
+        <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6408,8 +6413,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6469,7 +6479,7 @@
         <v>45387</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6530,7 +6540,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6544,10 +6554,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46301</v>
+        <v>45251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6560,7 +6570,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6613,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6620,7 +6630,7 @@
         <v>45251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6633,7 +6643,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6676,7 +6686,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6690,10 +6700,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46259</v>
+        <v>45744</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6705,13 +6715,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6759,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6773,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44951</v>
+        <v>46272</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6789,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6832,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6846,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45771</v>
+        <v>45188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6862,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6905,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6919,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44957</v>
+        <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6935,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6978,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6992,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45234</v>
+        <v>46286</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +7008,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7051,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7065,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44967</v>
+        <v>46244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7075,13 +7080,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45744</v>
+        <v>46287</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,8 +7153,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45699</v>
+        <v>46132</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7226,13 +7231,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44636</v>
+        <v>46259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7304,8 +7304,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7348,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7362,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45628</v>
+        <v>46301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7377,13 +7382,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,24 +7426,24 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45783</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7455,8 +7455,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7499,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7513,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7534,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7577,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7594,7 +7599,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7612,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7655,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7669,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7690,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>52.1</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7750,7 +7755,7 @@
         <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7828,7 +7833,7 @@
         <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7886,10 +7891,10 @@
       </c>
       <c r="V97" s="2" t="inlineStr"/>
     </row>
-    <row r="98" ht="15" customHeight="1">
+    <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4416-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7903,10 +7908,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7924,7 +7929,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>17.4</v>
+        <v>40</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -7963,84 +7968,6 @@
         <v>0</v>
       </c>
       <c r="V98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>S 4416-2023</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="n">
-        <v>45266</v>
-      </c>
-      <c r="E99" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>40</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="S99" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18303-2022</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44685</v>
+        <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1563,13 +1563,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 18303-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45188</v>
+        <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1641,8 +1636,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45197</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1714,13 +1714,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1763,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1777,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45771</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1793,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1836,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1850,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44648</v>
+        <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1865,8 +1860,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45679</v>
+        <v>45095</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44790</v>
+        <v>45000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,8 +2011,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2060,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45783</v>
+        <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2090,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45216</v>
+        <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2157,8 +2162,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45095</v>
+        <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2231,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2288,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44812</v>
+        <v>45903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2304,7 +2314,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2347,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2361,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45446</v>
+        <v>45216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2376,13 +2386,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2425,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44972</v>
+        <v>45919</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2455,7 +2460,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45903</v>
+        <v>45926</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2527,8 +2532,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2571,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2585,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44951</v>
+        <v>45446</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2598,6 +2608,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2644,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2658,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45644</v>
+        <v>45188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2674,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2717,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2727,14 +2742,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44957</v>
+        <v>45211</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2747,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2790,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2804,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45919</v>
+        <v>45958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2820,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2863,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2877,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45812</v>
+        <v>45272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2892,13 +2907,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2941,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2955,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44967</v>
+        <v>45960</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2970,13 +2980,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45272</v>
+        <v>45448</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45926</v>
+        <v>45968</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3121,13 +3126,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45234</v>
+        <v>45973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3199,8 +3199,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3248,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3262,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45471</v>
+        <v>45679</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3316,7 +3321,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3335,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45827</v>
+        <v>45975</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3345,13 +3350,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45958</v>
+        <v>46132</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.3</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45960</v>
+        <v>46132</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45968</v>
+        <v>45980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3569,8 +3569,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3613,7 +3618,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45973</v>
+        <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3642,13 +3647,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45628</v>
+        <v>46132</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3720,13 +3720,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3764,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3778,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45975</v>
+        <v>44972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3799,7 +3794,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3842,7 +3837,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3856,10 +3851,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45000</v>
+        <v>45716</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3871,13 +3866,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3920,7 +3910,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3934,10 +3924,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45716</v>
+        <v>45631</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3950,7 +3940,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3993,7 +3983,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4007,10 +3997,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45980</v>
+        <v>45827</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4024,11 +4014,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4071,7 +4061,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4085,10 +4075,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45827</v>
+        <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4100,13 +4090,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4149,7 +4134,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4163,10 +4148,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44516</v>
+        <v>45282</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4179,7 +4164,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4222,7 +4207,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4236,10 +4221,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44782</v>
+        <v>45181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4252,7 +4237,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4295,7 +4280,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4309,10 +4294,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46153</v>
+        <v>46044</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4324,13 +4309,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4353,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4367,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45251</v>
+        <v>44782</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4383,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4426,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4440,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45181</v>
+        <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4476,7 +4456,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4499,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4513,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44972</v>
+        <v>46153</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4548,8 +4528,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4609,7 +4594,7 @@
         <v>46161</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4670,7 +4655,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4684,10 +4669,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45000</v>
+        <v>46162</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4701,11 +4686,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4748,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4765,7 +4750,7 @@
         <v>46162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4783,7 +4768,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4826,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4843,7 +4828,7 @@
         <v>44972</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4856,7 +4841,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4899,7 +4884,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4913,10 +4898,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44972</v>
+        <v>45420</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4929,7 +4914,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4972,7 +4957,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4986,10 +4971,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46162</v>
+        <v>45188</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5001,13 +4986,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5050,7 +5030,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5064,10 +5044,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45448</v>
+        <v>45588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5080,7 +5060,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5123,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5137,10 +5117,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45631</v>
+        <v>44972</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5153,7 +5133,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5196,7 +5176,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5210,10 +5190,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45588</v>
+        <v>45471</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5226,7 +5206,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5269,7 +5249,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5283,10 +5263,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46044</v>
+        <v>45251</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5299,7 +5279,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5342,7 +5322,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5352,14 +5332,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45211</v>
+        <v>45387</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5369,6 +5349,11 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -5415,7 +5400,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5432,7 +5417,7 @@
         <v>46204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5450,7 +5435,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5493,7 +5478,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5507,10 +5492,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44727</v>
+        <v>46204</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5522,8 +5507,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5566,7 +5556,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5580,10 +5570,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46205</v>
+        <v>45251</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5586,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5639,7 +5629,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5656,7 +5646,7 @@
         <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5668,8 +5658,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5712,7 +5707,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5726,10 +5721,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45282</v>
+        <v>46205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5741,8 +5736,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5785,7 +5785,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5814,13 +5814,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5863,7 +5858,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5880,7 +5875,7 @@
         <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5892,13 +5887,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5941,7 +5931,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5955,10 +5945,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46205</v>
+        <v>44951</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5970,13 +5960,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +6004,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6018,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46132</v>
+        <v>45771</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6049,7 +6034,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6077,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6091,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46132</v>
+        <v>44957</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6122,7 +6107,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6150,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6164,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46132</v>
+        <v>45234</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6180,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6223,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6237,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45420</v>
+        <v>44967</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6267,8 +6252,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6301,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6315,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44636</v>
+        <v>46272</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6331,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6374,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6388,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45699</v>
+        <v>45744</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6413,13 +6403,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6447,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6472,14 +6457,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45387</v>
+        <v>45699</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6493,11 +6478,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6540,7 +6525,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6554,10 +6539,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45251</v>
+        <v>44636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6570,7 +6555,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6613,7 +6598,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6627,10 +6612,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45251</v>
+        <v>45628</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6642,8 +6627,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6686,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6700,10 +6690,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45744</v>
+        <v>45783</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6716,7 +6706,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6759,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6773,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46272</v>
+        <v>46287</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6788,8 +6778,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6832,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6846,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45188</v>
+        <v>46244</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6862,7 +6857,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6905,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6919,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45251</v>
+        <v>46286</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6935,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6978,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6992,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46286</v>
+        <v>45644</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7008,7 +7003,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46244</v>
+        <v>45812</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7080,8 +7075,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46287</v>
+        <v>46132</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,13 +7153,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46132</v>
+        <v>45827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7231,8 +7226,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46259</v>
+        <v>46301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7304,13 +7304,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7348,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7362,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46301</v>
+        <v>46259</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7382,8 +7377,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 18303-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44648</v>
+        <v>44685</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1563,8 +1563,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1612,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18303-2022</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1626,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44685</v>
+        <v>44648</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1636,13 +1641,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45216</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45095</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45197</v>
+        <v>45771</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,13 +1860,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1909,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45095</v>
+        <v>45420</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1939,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45000</v>
+        <v>44636</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,13 +2006,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2060,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44790</v>
+        <v>45699</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2089,8 +2079,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2133,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45000</v>
+        <v>44972</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2162,13 +2157,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44972</v>
+        <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,7 +2231,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2294,14 +2284,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45903</v>
+        <v>45387</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2313,8 +2303,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2352,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2366,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45216</v>
+        <v>45251</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2382,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45919</v>
+        <v>45251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2455,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2498,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2512,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45926</v>
+        <v>45446</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2538,7 +2533,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45446</v>
+        <v>45744</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2610,13 +2605,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2676,7 +2666,7 @@
         <v>45188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2732,7 +2722,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2742,14 +2732,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45211</v>
+        <v>44951</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2752,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2795,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2819,10 +2809,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45958</v>
+        <v>44957</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2835,7 +2825,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2868,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2882,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45272</v>
+        <v>44967</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2907,8 +2897,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45960</v>
+        <v>45272</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2976,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45448</v>
+        <v>45234</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45968</v>
+        <v>45251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3122,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3165,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3179,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45973</v>
+        <v>45679</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3199,13 +3194,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3248,7 +3238,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3262,10 +3252,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45679</v>
+        <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3278,7 +3268,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3311,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3325,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45975</v>
+        <v>45471</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3351,7 +3341,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3394,7 +3384,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3398,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46132</v>
+        <v>45783</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3424,7 +3414,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3467,7 +3457,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3481,10 +3471,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46132</v>
+        <v>45919</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3497,7 +3487,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3540,7 +3530,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,10 +3544,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45980</v>
+        <v>45926</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3571,11 +3561,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3618,7 +3608,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3632,10 +3622,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44812</v>
+        <v>45000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3647,8 +3637,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3691,7 +3686,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46132</v>
+        <v>45628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3720,8 +3715,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44972</v>
+        <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45716</v>
+        <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3866,8 +3866,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3910,7 +3915,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3924,10 +3929,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45631</v>
+        <v>44782</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3940,7 +3945,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3983,7 +3988,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3997,10 +4002,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45827</v>
+        <v>45251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4012,13 +4017,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4061,7 +4061,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44516</v>
+        <v>45827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4090,8 +4090,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4134,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4148,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45282</v>
+        <v>44972</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4164,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4207,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4221,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45181</v>
+        <v>45958</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4237,7 +4242,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4280,7 +4285,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4294,10 +4299,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46044</v>
+        <v>45960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4310,7 +4315,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4353,7 +4358,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4367,10 +4372,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44782</v>
+        <v>45181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4383,7 +4388,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4426,7 +4431,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4440,10 +4445,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44727</v>
+        <v>45000</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4455,8 +4460,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4499,7 +4509,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4513,10 +4523,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46153</v>
+        <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4528,13 +4538,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>8.5</v>
+        <v>0.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4577,7 +4582,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4591,10 +4596,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46161</v>
+        <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4606,13 +4611,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46162</v>
+        <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4684,13 +4684,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4733,7 +4728,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4742,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46162</v>
+        <v>45973</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4764,11 +4759,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4806,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4820,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44972</v>
+        <v>45448</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4841,7 +4836,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4884,7 +4879,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4898,10 +4893,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45420</v>
+        <v>45975</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4914,7 +4909,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4974,7 +4969,7 @@
         <v>45188</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5030,7 +5025,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5044,10 +5039,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45588</v>
+        <v>45980</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5059,8 +5054,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5103,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44972</v>
+        <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5132,8 +5132,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5176,7 +5181,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5190,10 +5195,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45471</v>
+        <v>45631</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5206,7 +5211,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5249,7 +5254,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5259,14 +5264,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45251</v>
+        <v>45211</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5279,7 +5284,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5322,7 +5327,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5332,14 +5337,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45387</v>
+        <v>44790</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5351,13 +5356,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46204</v>
+        <v>46132</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5429,13 +5429,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>9.4</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46204</v>
+        <v>46132</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5507,13 +5502,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5556,7 +5546,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5570,10 +5560,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45251</v>
+        <v>46132</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5586,7 +5576,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5629,7 +5619,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5643,10 +5633,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46205</v>
+        <v>44727</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5658,13 +5648,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5707,7 +5692,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5721,10 +5706,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46205</v>
+        <v>45282</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5736,13 +5721,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5785,7 +5765,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5799,10 +5779,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46205</v>
+        <v>45716</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5815,7 +5795,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5858,7 +5838,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5872,10 +5852,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46205</v>
+        <v>45827</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5887,8 +5867,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5931,7 +5916,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5945,10 +5930,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44951</v>
+        <v>46044</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5961,7 +5946,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6004,7 +5989,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6018,10 +6003,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45771</v>
+        <v>44516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6034,7 +6019,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6077,7 +6062,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6091,10 +6076,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44957</v>
+        <v>46153</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6106,8 +6091,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>8.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6150,7 +6140,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6164,10 +6154,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45234</v>
+        <v>46161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6179,8 +6169,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6223,7 +6218,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6237,10 +6232,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44967</v>
+        <v>46162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6254,11 +6249,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6301,7 +6296,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6315,10 +6310,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46272</v>
+        <v>46162</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6330,8 +6325,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6374,7 +6374,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45744</v>
+        <v>45588</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6461,10 +6461,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45699</v>
+        <v>46204</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6478,11 +6478,11 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6525,7 +6525,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44636</v>
+        <v>46205</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6598,7 +6598,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45628</v>
+        <v>46205</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6627,13 +6627,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6676,7 +6671,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6690,10 +6685,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45783</v>
+        <v>46204</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6705,8 +6700,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>9.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46287</v>
+        <v>46205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6856,8 +6856,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6905,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6919,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46286</v>
+        <v>46272</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6935,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6978,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6992,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45644</v>
+        <v>46286</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7003,7 +7008,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7046,7 +7051,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7060,10 +7065,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45812</v>
+        <v>46244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7075,13 +7080,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46132</v>
+        <v>46287</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,8 +7153,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45827</v>
+        <v>46132</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7226,13 +7231,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46301</v>
+        <v>46259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7304,8 +7304,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7348,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7362,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46259</v>
+        <v>46301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7377,13 +7382,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44685</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44648</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45216</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45095</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45771</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45420</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>44636</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45699</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44972</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45387</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45251</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>45446</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45744</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>45188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>44951</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44957</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44967</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45272</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45234</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45679</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45471</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45783</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45919</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45926</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>44782</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>45251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>44972</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45958</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45000</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45973</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45448</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>45975</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45188</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>45980</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45631</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45211</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44790</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>46132</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>46132</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>46132</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44727</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45282</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45716</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45827</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46044</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>46153</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>46161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>46162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>46162</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45588</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>46204</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>46205</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>46205</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>46204</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>46205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46205</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>46272</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>46286</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>46244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46287</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>46132</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>46259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>46301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44685</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44648</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45216</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45095</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45771</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45420</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>44636</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45699</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44972</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45387</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45251</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>45251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>45446</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45744</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>45188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>44951</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>44957</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44967</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45272</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45234</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45679</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45903</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45471</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>45783</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45919</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>45926</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>45000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45628</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45812</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>44782</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>45251</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>44972</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45958</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45000</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44972</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45973</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45448</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>45975</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>45188</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>45980</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45197</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45631</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45211</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44790</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>46132</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>46132</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>46132</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44727</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>45282</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>45716</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45827</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>46044</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>44516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>46153</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>46161</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>46162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>46162</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45588</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>46204</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>46205</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>46205</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>46204</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>46205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46205</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>46272</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>46286</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>46244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>46287</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>46132</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>46259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>46301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18303-2022</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44685</v>
+        <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1563,13 +1563,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1612,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 18303-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44648</v>
+        <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1641,8 +1636,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45216</v>
+        <v>44951</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45095</v>
+        <v>45771</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45771</v>
+        <v>45903</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45420</v>
+        <v>44957</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44636</v>
+        <v>45234</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45699</v>
+        <v>45919</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2079,13 +2079,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2123,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2137,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44972</v>
+        <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2157,8 +2152,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44812</v>
+        <v>44967</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2230,8 +2230,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2279,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2284,14 +2289,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45387</v>
+        <v>45588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2303,13 +2308,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45251</v>
+        <v>45744</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45251</v>
+        <v>45699</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2454,8 +2454,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45446</v>
+        <v>44636</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2527,13 +2532,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45744</v>
+        <v>45628</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2605,8 +2605,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45188</v>
+        <v>45958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2679,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>7.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2722,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2736,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44951</v>
+        <v>45960</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2752,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2795,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2809,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44957</v>
+        <v>45783</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2825,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2868,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2882,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44967</v>
+        <v>46204</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>9.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45272</v>
+        <v>45968</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45234</v>
+        <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3048,8 +3053,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3102,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3116,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45251</v>
+        <v>46204</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3121,8 +3131,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3165,7 +3180,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3179,10 +3194,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45679</v>
+        <v>45975</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3195,7 +3210,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3238,7 +3253,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3252,10 +3267,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45903</v>
+        <v>46205</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3267,8 +3282,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3311,7 +3331,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3325,10 +3345,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45471</v>
+        <v>46205</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3340,8 +3360,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3384,7 +3409,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3398,10 +3423,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45783</v>
+        <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3414,7 +3439,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3457,7 +3482,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3471,10 +3496,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45919</v>
+        <v>46205</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3487,7 +3512,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3530,7 +3555,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3544,10 +3569,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45926</v>
+        <v>45980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3561,11 +3586,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3608,7 +3633,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3622,10 +3647,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45000</v>
+        <v>46272</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3637,13 +3662,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3686,7 +3706,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3700,10 +3720,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45628</v>
+        <v>45644</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3715,13 +3735,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3764,7 +3779,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3778,10 +3793,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45644</v>
+        <v>45812</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3793,8 +3808,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3837,7 +3857,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3851,10 +3871,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45812</v>
+        <v>45827</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3868,11 +3888,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3915,7 +3935,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3929,10 +3949,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44782</v>
+        <v>46044</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3945,7 +3965,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3988,7 +4008,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4002,10 +4022,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45251</v>
+        <v>46287</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4017,8 +4037,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4061,7 +4086,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4075,10 +4100,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45827</v>
+        <v>46244</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4090,13 +4115,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4159,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4173,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44972</v>
+        <v>46286</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4169,7 +4189,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4212,7 +4232,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4226,10 +4246,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45958</v>
+        <v>46132</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4242,7 +4262,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7.3</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4305,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,10 +4319,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45960</v>
+        <v>45251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4315,7 +4335,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4358,7 +4378,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4372,10 +4392,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45181</v>
+        <v>45251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4388,7 +4408,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4431,7 +4451,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4445,10 +4465,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45000</v>
+        <v>46301</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4460,13 +4480,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4509,7 +4524,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4523,10 +4538,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44972</v>
+        <v>45197</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4538,8 +4553,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4582,7 +4602,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4596,10 +4616,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44972</v>
+        <v>46132</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4612,7 +4632,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4655,7 +4675,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4669,10 +4689,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45968</v>
+        <v>46132</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4685,7 +4705,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4728,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4742,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45973</v>
+        <v>46259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4763,7 +4783,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4806,7 +4826,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4820,10 +4840,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45448</v>
+        <v>46132</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4836,7 +4856,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4879,7 +4899,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4893,10 +4913,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45975</v>
+        <v>45716</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4909,7 +4929,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4952,7 +4972,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4966,10 +4986,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45188</v>
+        <v>45095</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4982,7 +5002,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5025,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5039,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45980</v>
+        <v>45827</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5056,11 +5076,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5103,7 +5123,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5117,10 +5137,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45197</v>
+        <v>45000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5138,7 +5158,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5181,7 +5201,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5195,10 +5215,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45631</v>
+        <v>44516</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5211,7 +5231,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5254,7 +5274,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5264,14 +5284,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45211</v>
+        <v>44790</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5284,7 +5304,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5327,7 +5347,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5341,10 +5361,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44790</v>
+        <v>45000</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5356,8 +5376,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5400,7 +5425,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5414,10 +5439,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5429,8 +5454,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5473,7 +5503,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5487,10 +5517,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46132</v>
+        <v>44972</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5503,7 +5533,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5546,7 +5576,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5560,10 +5590,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5575,8 +5605,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5619,7 +5654,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5633,10 +5668,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44727</v>
+        <v>46162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5648,8 +5683,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5692,7 +5732,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5706,10 +5746,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45282</v>
+        <v>46162</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5721,8 +5761,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5765,7 +5810,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5779,10 +5824,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45716</v>
+        <v>45216</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5795,7 +5840,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5838,7 +5883,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5852,10 +5897,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45827</v>
+        <v>45446</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5873,7 +5918,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5916,7 +5961,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5930,10 +5975,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46044</v>
+        <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5946,7 +5991,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5989,7 +6034,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5999,14 +6044,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44516</v>
+        <v>45211</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6019,7 +6064,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6062,7 +6107,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6076,10 +6121,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46153</v>
+        <v>45272</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6091,13 +6136,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6140,7 +6180,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6154,10 +6194,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46161</v>
+        <v>45448</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6169,13 +6209,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6218,7 +6253,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6232,10 +6267,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46162</v>
+        <v>45679</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6247,13 +6282,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6296,7 +6326,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6310,10 +6340,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46162</v>
+        <v>44812</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6325,13 +6355,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6374,7 +6399,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6388,10 +6413,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45588</v>
+        <v>44972</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6404,7 +6429,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6447,7 +6472,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6461,10 +6486,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46204</v>
+        <v>45631</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6476,13 +6501,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6525,7 +6545,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6539,10 +6559,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46205</v>
+        <v>45282</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6555,7 +6575,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6598,7 +6618,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6612,10 +6632,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46205</v>
+        <v>45181</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6628,7 +6648,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6671,7 +6691,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6685,10 +6705,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46204</v>
+        <v>44782</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6700,13 +6720,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6764,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6778,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46205</v>
+        <v>44727</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6778,13 +6793,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6837,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6851,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46205</v>
+        <v>44972</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6856,13 +6866,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6905,7 +6910,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6919,10 +6924,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46272</v>
+        <v>45420</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6935,7 +6940,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6978,7 +6983,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6992,10 +6997,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46286</v>
+        <v>45188</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7008,7 +7013,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7056,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7070,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46244</v>
+        <v>44972</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7129,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7143,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46287</v>
+        <v>45471</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,13 +7158,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46132</v>
+        <v>45251</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7285,14 +7285,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46259</v>
+        <v>45387</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46301</v>
+        <v>45251</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44951</v>
+        <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45771</v>
+        <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45903</v>
+        <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44957</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1933,8 +1933,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1977,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45234</v>
+        <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2050,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2064,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45919</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2080,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2123,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2137,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45926</v>
+        <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2152,13 +2157,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44967</v>
+        <v>45644</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2230,13 +2230,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2279,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45588</v>
+        <v>45812</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2308,8 +2303,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45744</v>
+        <v>45903</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45699</v>
+        <v>45919</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2454,13 +2454,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2498,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2512,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44636</v>
+        <v>45827</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2532,8 +2527,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45628</v>
+        <v>45926</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45958</v>
+        <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45960</v>
+        <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45783</v>
+        <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46204</v>
+        <v>45000</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>9.4</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>45968</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46204</v>
+        <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3131,13 +3131,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3180,7 +3175,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45975</v>
+        <v>44782</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3253,7 +3248,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3267,10 +3262,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46205</v>
+        <v>45980</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3284,11 +3279,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3331,7 +3326,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3345,10 +3340,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46205</v>
+        <v>45251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3360,13 +3355,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3409,7 +3399,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3423,10 +3413,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46205</v>
+        <v>44972</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3439,7 +3429,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3482,7 +3472,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3496,10 +3486,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46205</v>
+        <v>45000</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3511,8 +3501,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3555,7 +3550,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3569,10 +3564,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45980</v>
+        <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3584,13 +3579,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3633,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3647,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46272</v>
+        <v>44972</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3663,7 +3653,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3706,7 +3696,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3720,10 +3710,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45644</v>
+        <v>45188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3736,7 +3726,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3779,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3793,10 +3783,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45812</v>
+        <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3810,7 +3800,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3857,7 +3847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3871,10 +3861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45827</v>
+        <v>44790</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3886,13 +3876,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3935,7 +3920,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3949,10 +3934,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46044</v>
+        <v>46132</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3965,7 +3950,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4008,7 +3993,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4022,10 +4007,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46287</v>
+        <v>46132</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4037,13 +4022,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4086,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4100,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46244</v>
+        <v>46132</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4116,7 +4096,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4159,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4173,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46286</v>
+        <v>45095</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4189,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4232,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4246,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46132</v>
+        <v>44972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4262,7 +4242,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4305,7 +4285,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4319,10 +4299,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45251</v>
+        <v>44967</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4334,8 +4314,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4378,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4392,10 +4377,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45251</v>
+        <v>45716</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4408,7 +4393,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4451,7 +4436,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4465,10 +4450,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46301</v>
+        <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4481,7 +4466,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4524,7 +4509,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4538,10 +4523,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45197</v>
+        <v>45827</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4559,7 +4544,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4602,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4616,10 +4601,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46132</v>
+        <v>44516</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4632,7 +4617,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4675,7 +4660,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4689,10 +4674,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46132</v>
+        <v>45471</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4705,7 +4690,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4748,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4762,10 +4747,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46259</v>
+        <v>46153</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4783,7 +4768,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4826,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4840,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4855,8 +4840,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4899,7 +4889,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4913,10 +4903,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45716</v>
+        <v>46162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4928,8 +4918,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4972,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4986,10 +4981,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45095</v>
+        <v>45628</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5001,8 +4996,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45827</v>
+        <v>46162</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5076,11 +5076,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45000</v>
+        <v>45181</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5152,13 +5152,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5201,7 +5196,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5215,10 +5210,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44516</v>
+        <v>45588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5231,7 +5226,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5274,7 +5269,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5288,10 +5283,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44790</v>
+        <v>45448</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5304,7 +5299,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5347,7 +5342,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5361,10 +5356,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45000</v>
+        <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5376,13 +5371,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5425,7 +5415,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5435,14 +5425,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46153</v>
+        <v>45211</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5454,13 +5444,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5503,7 +5488,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5517,10 +5502,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44972</v>
+        <v>46204</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5532,8 +5517,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.2</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5576,7 +5566,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5590,10 +5580,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46161</v>
+        <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5605,13 +5595,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5654,7 +5639,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5668,10 +5653,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46162</v>
+        <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5683,13 +5668,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5732,7 +5712,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5746,10 +5726,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46162</v>
+        <v>46204</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5763,11 +5743,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>9.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5810,7 +5790,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5824,10 +5804,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45216</v>
+        <v>46205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5839,8 +5819,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5883,7 +5868,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5897,10 +5882,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45446</v>
+        <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5918,7 +5903,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5961,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5975,10 +5960,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45188</v>
+        <v>44727</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5991,7 +5976,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6034,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6044,14 +6029,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45211</v>
+        <v>46272</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6064,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6107,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6121,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45272</v>
+        <v>45282</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6137,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6180,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6194,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45448</v>
+        <v>45420</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6210,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6253,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6267,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45679</v>
+        <v>44636</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6283,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6326,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6340,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44812</v>
+        <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6355,8 +6340,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6399,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6413,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44972</v>
+        <v>46286</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6429,7 +6419,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6472,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6486,10 +6476,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45631</v>
+        <v>46244</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6502,7 +6492,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6545,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6555,14 +6545,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45282</v>
+        <v>45387</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6574,8 +6564,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6618,7 +6613,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6632,10 +6627,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45181</v>
+        <v>46287</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6647,8 +6642,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44782</v>
+        <v>45251</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44727</v>
+        <v>45251</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6837,7 +6837,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44972</v>
+        <v>45744</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45420</v>
+        <v>45188</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45188</v>
+        <v>45251</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44972</v>
+        <v>45679</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7129,7 +7129,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45471</v>
+        <v>46132</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45251</v>
+        <v>45783</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7285,14 +7285,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45387</v>
+        <v>46259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45251</v>
+        <v>46301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44648</v>
+        <v>45272</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 18303-2022</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44685</v>
+        <v>44648</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1636,13 +1636,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1685,7 +1680,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45771</v>
+        <v>45448</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1710,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1753,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 18303-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1767,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>44685</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1787,8 +1782,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44812</v>
+        <v>45644</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>45812</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44951</v>
+        <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>45827</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2084,8 +2084,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45234</v>
+        <v>45903</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2158,7 +2163,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2206,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45644</v>
+        <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2231,7 +2236,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2279,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2288,10 +2293,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45812</v>
+        <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2303,13 +2308,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45903</v>
+        <v>45251</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45919</v>
+        <v>45251</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45827</v>
+        <v>45919</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2525,11 +2525,6 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2593,7 +2588,7 @@
         <v>45926</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2654,7 +2649,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46044</v>
+        <v>45197</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2683,8 +2678,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45958</v>
+        <v>45095</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45960</v>
+        <v>45958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45000</v>
+        <v>45960</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2902,13 +2902,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45968</v>
+        <v>45000</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2980,8 +2975,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45973</v>
+        <v>45968</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3053,13 +3053,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3102,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3116,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45975</v>
+        <v>45973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3131,8 +3126,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44782</v>
+        <v>45975</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45980</v>
+        <v>45631</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3277,13 +3277,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3326,7 +3321,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3340,10 +3335,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45251</v>
+        <v>45980</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3355,8 +3350,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44972</v>
+        <v>44790</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>45000</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44972</v>
+        <v>46132</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3696,7 +3696,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45188</v>
+        <v>46132</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45197</v>
+        <v>46132</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3798,13 +3798,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3847,7 +3842,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3861,10 +3856,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44790</v>
+        <v>45716</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3877,7 +3872,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3920,7 +3915,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3934,10 +3929,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46132</v>
+        <v>45216</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3950,7 +3945,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3993,7 +3988,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4007,10 +4002,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46132</v>
+        <v>45827</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4022,8 +4017,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46132</v>
+        <v>46044</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45095</v>
+        <v>44516</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44972</v>
+        <v>45446</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4241,8 +4241,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4290,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,10 +4304,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44967</v>
+        <v>45188</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4314,13 +4319,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4373,14 +4373,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45716</v>
+        <v>45211</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4436,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45272</v>
+        <v>46153</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4465,8 +4465,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4509,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4523,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45827</v>
+        <v>45282</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4538,13 +4543,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4587,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44516</v>
+        <v>45181</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4660,7 +4660,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45471</v>
+        <v>46161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4689,8 +4689,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4733,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4764,11 +4769,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4816,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4830,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46161</v>
+        <v>44782</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4840,13 +4845,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4906,7 +4906,7 @@
         <v>46162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45628</v>
+        <v>44727</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4996,13 +4996,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5045,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46162</v>
+        <v>45588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5074,13 +5069,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5123,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5137,10 +5127,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45181</v>
+        <v>46204</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5152,8 +5142,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>9.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5196,7 +5191,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5210,10 +5205,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45588</v>
+        <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5225,8 +5220,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5269,7 +5269,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45448</v>
+        <v>44972</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5342,7 +5342,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45631</v>
+        <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5371,8 +5371,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5415,7 +5420,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5425,14 +5430,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45211</v>
+        <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5444,8 +5449,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5488,7 +5498,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5502,10 +5512,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5515,11 +5525,6 @@
       <c r="G66" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -5566,7 +5571,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5583,7 +5588,7 @@
         <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5601,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5639,7 +5644,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5653,10 +5658,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46205</v>
+        <v>45420</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5669,7 +5674,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5712,7 +5717,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5726,10 +5731,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46204</v>
+        <v>45188</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5741,13 +5746,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46205</v>
+        <v>46272</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5819,13 +5819,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5868,7 +5863,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5882,10 +5877,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46205</v>
+        <v>44972</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5897,13 +5892,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5936,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5960,10 +5950,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44727</v>
+        <v>45471</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5976,7 +5966,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +6009,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6023,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46272</v>
+        <v>45251</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6049,7 +6039,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6082,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6102,14 +6092,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45282</v>
+        <v>45387</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6121,8 +6111,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6160,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6174,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45420</v>
+        <v>46287</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6194,8 +6189,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44636</v>
+        <v>46244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45699</v>
+        <v>45251</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6340,13 +6340,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6406,7 +6401,7 @@
         <v>46286</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6462,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6476,10 +6471,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46244</v>
+        <v>44951</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6492,7 +6487,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6530,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6545,14 +6540,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45387</v>
+        <v>45771</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6564,13 +6559,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6613,7 +6603,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6627,10 +6617,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46287</v>
+        <v>44957</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6642,13 +6632,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6691,7 +6676,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6705,10 +6690,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45251</v>
+        <v>45234</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6721,7 +6706,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6764,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6778,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45251</v>
+        <v>46132</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6794,7 +6779,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6837,7 +6822,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6851,10 +6836,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45744</v>
+        <v>44967</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6866,8 +6851,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6910,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6924,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45188</v>
+        <v>45744</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6940,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6983,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6997,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45251</v>
+        <v>45699</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7012,8 +7002,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7056,7 +7051,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7070,10 +7065,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45679</v>
+        <v>46301</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7086,7 +7081,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7129,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7143,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46132</v>
+        <v>44636</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7202,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45783</v>
+        <v>45628</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7231,8 +7226,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7292,7 +7292,7 @@
         <v>46259</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46301</v>
+        <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 13572-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45272</v>
+        <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1607,7 +1607,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 13572-2022</t>
+          <t>A 18303-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44648</v>
+        <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1636,8 +1636,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1680,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45448</v>
+        <v>44790</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1753,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 18303-2022</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1767,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44685</v>
+        <v>45771</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1782,13 +1787,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>45644</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45812</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45679</v>
+        <v>45216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>45827</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45903</v>
+        <v>45095</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>44812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44972</v>
+        <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2308,8 +2308,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2352,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2366,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45251</v>
+        <v>44972</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2382,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2425,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45251</v>
+        <v>44951</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2455,7 +2460,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45919</v>
+        <v>44957</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2528,7 +2533,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2571,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2585,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45926</v>
+        <v>45234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2600,13 +2605,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2649,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45197</v>
+        <v>44967</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45095</v>
+        <v>45272</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45958</v>
+        <v>45471</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45960</v>
+        <v>46132</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45000</v>
+        <v>46132</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2975,13 +2975,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45968</v>
+        <v>46132</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45973</v>
+        <v>45000</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3132,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3175,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3189,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45975</v>
+        <v>44782</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3248,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3262,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3277,8 +3272,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45980</v>
+        <v>45251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3350,13 +3350,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3399,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3413,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44790</v>
+        <v>45716</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3429,7 +3424,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3472,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45000</v>
+        <v>45903</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3501,13 +3496,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3550,7 +3540,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3567,7 +3557,7 @@
         <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3580,7 +3570,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3623,7 +3613,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3637,10 +3627,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46132</v>
+        <v>45827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3652,8 +3642,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3696,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46132</v>
+        <v>45000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3725,8 +3720,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46132</v>
+        <v>44972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>0.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45716</v>
+        <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45216</v>
+        <v>44516</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45827</v>
+        <v>45181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4017,13 +4017,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4066,7 +4061,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4075,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46044</v>
+        <v>46153</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4095,8 +4090,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>4.8</v>
+        <v>8.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44516</v>
+        <v>45188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45446</v>
+        <v>45448</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4241,13 +4241,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4290,7 +4285,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4304,10 +4299,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45188</v>
+        <v>45197</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4319,8 +4314,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4373,14 +4373,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45211</v>
+        <v>45919</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4436,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4467,11 +4467,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45282</v>
+        <v>46162</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4543,8 +4543,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4587,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4601,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45181</v>
+        <v>46162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4616,8 +4621,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4660,7 +4670,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4674,10 +4684,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46161</v>
+        <v>45926</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4691,11 +4701,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46162</v>
+        <v>45631</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4767,13 +4777,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4816,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4826,14 +4831,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44782</v>
+        <v>45211</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4846,7 +4851,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46162</v>
+        <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4918,13 +4923,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         <v>44727</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45588</v>
+        <v>45282</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5130,7 +5130,7 @@
         <v>46204</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5191,7 +5191,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5205,10 +5205,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5218,11 +5218,6 @@
       <c r="G62" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -5269,7 +5264,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5283,10 +5278,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44972</v>
+        <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5299,7 +5294,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5342,7 +5337,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5356,10 +5351,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5377,7 +5372,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5420,7 +5415,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5437,7 +5432,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5455,7 +5450,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5498,7 +5493,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5515,7 +5510,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5527,8 +5522,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46205</v>
+        <v>45958</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45420</v>
+        <v>46272</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45188</v>
+        <v>45960</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46272</v>
+        <v>45420</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44972</v>
+        <v>44636</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45471</v>
+        <v>45699</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5965,8 +5965,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6009,7 +6014,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6019,14 +6024,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45251</v>
+        <v>45387</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6038,8 +6043,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6082,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6092,14 +6102,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45387</v>
+        <v>45968</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6111,13 +6121,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6160,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6174,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46287</v>
+        <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6189,13 +6194,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46244</v>
+        <v>45251</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45251</v>
+        <v>45744</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46286</v>
+        <v>45188</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44951</v>
+        <v>45973</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6486,8 +6486,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6530,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6544,10 +6549,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45771</v>
+        <v>46286</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6560,7 +6565,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6603,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6617,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44957</v>
+        <v>45975</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6633,7 +6638,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6676,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6690,10 +6695,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45234</v>
+        <v>46244</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6706,7 +6711,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46132</v>
+        <v>45980</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6778,8 +6783,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6822,7 +6832,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6836,10 +6846,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44967</v>
+        <v>46287</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6867,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6910,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6924,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45744</v>
+        <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6940,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6983,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6997,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45699</v>
+        <v>45679</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7002,13 +7012,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7056,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7070,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46301</v>
+        <v>45783</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7129,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7143,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44636</v>
+        <v>46132</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7197,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45628</v>
+        <v>46259</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7275,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46259</v>
+        <v>46301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7304,13 +7309,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45783</v>
+        <v>46044</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44790</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45771</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45644</v>
+        <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,8 +1860,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45812</v>
+        <v>45095</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1933,13 +1938,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45216</v>
+        <v>45000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,8 +2011,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2060,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45827</v>
+        <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2084,13 +2089,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45095</v>
+        <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2162,8 +2162,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2206,7 +2211,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2220,10 +2225,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44812</v>
+        <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2236,7 +2241,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2279,7 +2284,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45446</v>
+        <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2308,13 +2313,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44972</v>
+        <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2386,8 +2386,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44951</v>
+        <v>44516</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44957</v>
+        <v>45903</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45234</v>
+        <v>45919</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2606,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44967</v>
+        <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2689,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2732,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2746,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45272</v>
+        <v>45188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2762,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2810,14 +2815,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45471</v>
+        <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2830,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46132</v>
+        <v>45926</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2902,8 +2907,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2956,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2970,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2975,8 +2985,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>8.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3034,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3048,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46132</v>
+        <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3049,7 +3064,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3107,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3121,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45000</v>
+        <v>45448</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3121,13 +3136,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3180,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3194,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44782</v>
+        <v>45679</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3210,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3253,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3267,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45628</v>
+        <v>45958</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3272,13 +3282,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>7.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3326,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3340,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45251</v>
+        <v>45960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3351,7 +3356,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45716</v>
+        <v>46161</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3423,8 +3428,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3467,7 +3477,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3481,10 +3491,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45903</v>
+        <v>44812</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3497,7 +3507,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3557,7 +3567,7 @@
         <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3613,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3627,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45827</v>
+        <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3642,13 +3652,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3691,7 +3696,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3705,10 +3710,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45000</v>
+        <v>46162</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3722,11 +3727,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3774,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3788,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44972</v>
+        <v>45973</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3798,8 +3803,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3842,7 +3852,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3856,10 +3866,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44972</v>
+        <v>45975</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3872,7 +3882,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3915,7 +3925,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3929,10 +3939,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44516</v>
+        <v>46162</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3944,8 +3954,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3988,7 +4003,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4002,10 +4017,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45181</v>
+        <v>45980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4017,8 +4032,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4061,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4075,10 +4095,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46153</v>
+        <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4090,13 +4110,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4168,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45188</v>
+        <v>45282</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4169,7 +4184,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4212,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4226,10 +4241,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45448</v>
+        <v>45181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4242,7 +4257,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45197</v>
+        <v>44782</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4314,13 +4329,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4377,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45919</v>
+        <v>46044</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4393,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4450,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46161</v>
+        <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4465,13 +4475,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4514,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4528,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46162</v>
+        <v>45588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4543,13 +4548,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4592,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46162</v>
+        <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4621,13 +4621,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4670,7 +4665,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4684,10 +4679,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45926</v>
+        <v>46132</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4699,13 +4694,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4748,7 +4738,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4762,10 +4752,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45631</v>
+        <v>46132</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4778,7 +4768,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4821,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4831,14 +4821,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45211</v>
+        <v>46204</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4850,8 +4840,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45588</v>
+        <v>46132</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4924,7 +4919,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4962,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4976,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44727</v>
+        <v>46204</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4996,8 +4991,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45282</v>
+        <v>45420</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46204</v>
+        <v>45716</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5142,13 +5142,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5191,7 +5186,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5208,7 +5203,7 @@
         <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5220,8 +5215,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46205</v>
+        <v>45188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5337,7 +5337,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.4</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5432,7 +5432,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5444,13 +5444,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5493,7 +5488,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5510,7 +5505,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5522,13 +5517,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5571,7 +5561,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5585,10 +5575,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45958</v>
+        <v>44972</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5601,7 +5591,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.3</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5644,7 +5634,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5658,10 +5648,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46272</v>
+        <v>45471</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5674,7 +5664,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5717,7 +5707,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5731,10 +5721,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45960</v>
+        <v>45251</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5737,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5790,7 +5780,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5804,10 +5794,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45420</v>
+        <v>46272</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5810,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5863,7 +5853,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5873,14 +5863,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44636</v>
+        <v>45387</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5892,8 +5882,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5936,7 +5931,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5950,10 +5945,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45699</v>
+        <v>45251</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5965,13 +5960,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6014,7 +6004,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6024,14 +6014,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45387</v>
+        <v>44951</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6043,13 +6033,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6077,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6091,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45968</v>
+        <v>46287</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6121,8 +6106,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6165,7 +6155,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6169,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6185,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6228,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6242,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45251</v>
+        <v>46244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6258,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6301,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6315,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45744</v>
+        <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6331,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6374,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6388,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45188</v>
+        <v>44957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6414,7 +6404,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6447,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6461,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45973</v>
+        <v>45234</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6486,13 +6476,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6520,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6549,10 +6534,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46286</v>
+        <v>44967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6564,8 +6549,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6598,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6612,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45975</v>
+        <v>45744</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6638,7 +6628,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6671,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6695,10 +6685,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46244</v>
+        <v>45699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6710,8 +6700,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6749,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6763,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45980</v>
+        <v>46132</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6783,13 +6778,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6832,7 +6822,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6846,10 +6836,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46287</v>
+        <v>44636</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6861,13 +6851,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6910,7 +6895,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6924,10 +6909,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45251</v>
+        <v>45628</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6939,8 +6924,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6983,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6997,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45679</v>
+        <v>45783</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7013,7 +7003,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7056,7 +7046,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7070,10 +7060,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45783</v>
+        <v>46301</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7086,7 +7076,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7129,7 +7119,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7143,10 +7133,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46132</v>
+        <v>46259</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7158,8 +7148,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46259</v>
+        <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7231,13 +7226,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7270,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7284,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46301</v>
+        <v>45812</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7309,8 +7299,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7348,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7362,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46044</v>
+        <v>45827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7382,8 +7377,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>45095</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44516</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45903</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45919</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45926</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>46153</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45448</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45679</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45958</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46161</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>44812</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>46162</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45973</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45975</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>46162</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45282</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>45181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44782</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>46044</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>46132</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>46132</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>46204</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>46132</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>46204</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45420</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45716</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44972</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45471</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45251</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46272</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45387</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45251</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>44951</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>46287</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45771</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>46244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45234</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45744</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>46132</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44636</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45628</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45783</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>46301</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>46259</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45812</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>45095</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45000</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44790</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45000</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45216</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45827</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44516</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45903</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45919</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45211</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45926</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>46153</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45448</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45679</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45958</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46161</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>44812</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>46162</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45973</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45975</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>46162</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45282</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>45181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44782</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>46044</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44727</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44972</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>46132</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>46132</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>46204</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>46132</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>46204</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45420</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45716</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46205</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45188</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>44972</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45471</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45251</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46272</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45387</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45251</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>44951</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>46287</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45771</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>46244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>46286</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45234</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>44967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45744</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45699</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>46132</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44636</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45628</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45783</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>46301</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>46259</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45644</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45812</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45827</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45197</v>
+        <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,13 +1860,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1909,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45095</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1938,8 +1933,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45000</v>
+        <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,13 +2011,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2060,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44790</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2090,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2133,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45000</v>
+        <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2162,13 +2157,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2211,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2225,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44972</v>
+        <v>45000</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2240,8 +2230,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2284,7 +2279,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2298,10 +2293,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45216</v>
+        <v>45251</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2314,7 +2309,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2352,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2366,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45827</v>
+        <v>44782</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2386,13 +2381,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2435,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2449,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44516</v>
+        <v>44972</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2465,7 +2455,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2508,7 +2498,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2522,10 +2512,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45903</v>
+        <v>45000</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2537,8 +2527,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2581,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2595,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45919</v>
+        <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2611,7 +2606,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2649,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45446</v>
+        <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2683,13 +2678,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2732,7 +2722,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2746,10 +2736,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45188</v>
+        <v>45716</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2762,7 +2752,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2805,7 +2795,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2815,14 +2805,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45211</v>
+        <v>45827</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2834,8 +2824,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2873,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45926</v>
+        <v>45188</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2907,13 +2902,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2956,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2970,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46153</v>
+        <v>45903</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2985,13 +2975,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3034,7 +3019,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3048,10 +3033,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45272</v>
+        <v>44516</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3064,7 +3049,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3107,7 +3092,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3121,10 +3106,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45448</v>
+        <v>45197</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3136,8 +3121,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3180,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3194,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45679</v>
+        <v>45919</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3210,7 +3200,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3253,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3267,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45958</v>
+        <v>45926</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3282,8 +3272,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3326,7 +3321,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3340,10 +3335,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45960</v>
+        <v>44790</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3356,7 +3351,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3399,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3413,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46161</v>
+        <v>45095</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3428,13 +3423,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3477,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3491,10 +3481,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44812</v>
+        <v>45958</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3507,7 +3497,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>7.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3550,7 +3540,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3564,10 +3554,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44972</v>
+        <v>46153</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3579,8 +3569,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3623,7 +3618,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3637,10 +3632,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45968</v>
+        <v>45960</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3653,7 +3648,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3696,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46162</v>
+        <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3725,13 +3720,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3774,7 +3764,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3788,10 +3778,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45973</v>
+        <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3803,13 +3793,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3852,7 +3837,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3866,10 +3851,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45975</v>
+        <v>45973</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3881,8 +3866,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3925,7 +3915,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3939,10 +3929,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46162</v>
+        <v>45975</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3954,13 +3944,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4020,7 +4005,7 @@
         <v>45980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4081,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4095,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45631</v>
+        <v>44967</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4110,8 +4095,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4154,7 +4144,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4168,10 +4158,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45282</v>
+        <v>46161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4183,8 +4173,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4227,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4241,10 +4236,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45181</v>
+        <v>45272</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4257,7 +4252,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4295,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4309,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44782</v>
+        <v>46162</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4329,8 +4324,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46044</v>
+        <v>45471</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44727</v>
+        <v>46162</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4475,8 +4475,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4524,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4538,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45588</v>
+        <v>46044</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4549,7 +4554,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4592,7 +4597,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4606,10 +4611,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44972</v>
+        <v>45628</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4621,8 +4626,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4665,7 +4675,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4679,10 +4689,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46132</v>
+        <v>45588</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4695,7 +4705,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4738,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4752,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46132</v>
+        <v>45181</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4768,7 +4778,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4835,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46204</v>
+        <v>45448</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4840,13 +4850,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>9.4</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4889,7 +4894,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4903,10 +4908,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46132</v>
+        <v>45631</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4919,7 +4924,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4962,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4972,14 +4977,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46204</v>
+        <v>45211</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4991,13 +4996,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45420</v>
+        <v>46132</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45716</v>
+        <v>46132</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5186,7 +5186,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5215,13 +5215,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5264,7 +5259,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5278,10 +5273,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45188</v>
+        <v>46204</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5293,8 +5288,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5337,7 +5337,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5354,7 +5354,7 @@
         <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5366,13 +5366,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5415,7 +5410,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5432,7 +5427,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5445,7 +5440,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5488,7 +5483,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5502,10 +5497,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5517,8 +5512,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>9.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44972</v>
+        <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5590,8 +5590,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5634,7 +5639,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5648,10 +5653,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45471</v>
+        <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5663,8 +5668,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5707,7 +5717,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5721,10 +5731,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45251</v>
+        <v>44727</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5737,7 +5747,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5780,7 +5790,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5794,10 +5804,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46272</v>
+        <v>45282</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5810,7 +5820,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5853,7 +5863,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5863,14 +5873,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45387</v>
+        <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5882,13 +5892,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5931,7 +5936,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5945,10 +5950,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45251</v>
+        <v>44636</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5961,7 +5966,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6004,7 +6009,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6018,10 +6023,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44951</v>
+        <v>46286</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6034,7 +6039,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6077,7 +6082,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6091,10 +6096,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46287</v>
+        <v>46244</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6106,13 +6111,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45771</v>
+        <v>45699</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6184,8 +6184,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6228,7 +6233,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6242,10 +6247,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6257,8 +6262,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6301,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6311,14 +6321,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46286</v>
+        <v>45387</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6330,8 +6340,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6374,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6388,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44957</v>
+        <v>45251</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6447,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6461,10 +6476,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45234</v>
+        <v>45251</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6477,7 +6492,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6520,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6534,10 +6549,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44967</v>
+        <v>45744</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6549,13 +6564,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6598,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6612,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45744</v>
+        <v>45188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6628,7 +6638,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6671,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6685,10 +6695,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45699</v>
+        <v>45251</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6700,13 +6710,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6749,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6763,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46132</v>
+        <v>45679</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6779,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6822,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6836,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44636</v>
+        <v>46132</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6895,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6909,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45628</v>
+        <v>45783</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6924,13 +6929,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45783</v>
+        <v>46259</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7002,8 +7002,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7063,7 +7068,7 @@
         <v>46301</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7119,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7133,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46259</v>
+        <v>45644</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7148,13 +7153,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7197,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7211,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45644</v>
+        <v>45812</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7226,8 +7226,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7270,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7284,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45812</v>
+        <v>45827</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7301,11 +7306,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7348,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7362,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45827</v>
+        <v>46272</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7377,13 +7382,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45771</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>45251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44812</v>
+        <v>45644</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>45812</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44951</v>
+        <v>45197</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,8 +2011,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2060,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>45903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2090,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45234</v>
+        <v>46044</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2158,7 +2163,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2206,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45000</v>
+        <v>45919</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2230,13 +2235,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45251</v>
+        <v>45926</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2308,8 +2308,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2352,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2366,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44782</v>
+        <v>45095</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2382,7 +2387,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2425,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44972</v>
+        <v>45000</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2454,8 +2459,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45000</v>
+        <v>45827</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2543,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2586,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2600,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44972</v>
+        <v>44790</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2606,7 +2616,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2659,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2673,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44972</v>
+        <v>45000</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2678,8 +2688,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2722,7 +2737,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2736,10 +2751,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45716</v>
+        <v>45958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2752,7 +2767,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>7.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2795,7 +2810,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2809,10 +2824,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45827</v>
+        <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2824,13 +2839,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2873,7 +2883,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2887,10 +2897,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45188</v>
+        <v>44972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2903,7 +2913,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2956,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2960,10 +2970,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45903</v>
+        <v>45968</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2976,7 +2986,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3019,7 +3029,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3033,10 +3043,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44516</v>
+        <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3048,8 +3058,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3092,7 +3107,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3106,10 +3121,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45197</v>
+        <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3121,13 +3136,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3180,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3194,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45919</v>
+        <v>46132</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3210,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3253,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3267,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45926</v>
+        <v>46132</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3272,13 +3282,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3321,7 +3326,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3335,10 +3340,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44790</v>
+        <v>45980</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3350,8 +3355,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3394,7 +3404,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3418,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45095</v>
+        <v>46132</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3424,7 +3434,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3467,7 +3477,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3481,10 +3491,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45958</v>
+        <v>45216</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3497,7 +3507,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3540,7 +3550,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,10 +3564,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46153</v>
+        <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3569,13 +3579,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>8.5</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3618,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3632,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45960</v>
+        <v>45827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3647,8 +3652,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3691,7 +3701,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44972</v>
+        <v>44516</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3764,7 +3774,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3778,10 +3788,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45968</v>
+        <v>45446</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3793,8 +3803,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3837,7 +3852,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3851,10 +3866,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45973</v>
+        <v>45188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3866,13 +3881,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3915,7 +3925,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3925,14 +3935,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45975</v>
+        <v>45211</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3945,7 +3955,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3988,7 +3998,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4002,10 +4012,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45980</v>
+        <v>45272</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4017,13 +4027,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4066,7 +4071,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4085,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44967</v>
+        <v>45448</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4095,13 +4100,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4144,7 +4144,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46161</v>
+        <v>45679</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4173,13 +4173,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4222,7 +4217,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4236,10 +4231,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45272</v>
+        <v>46153</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4251,8 +4246,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4295,7 +4295,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46162</v>
+        <v>44812</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4324,13 +4324,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4368,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4382,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45471</v>
+        <v>44972</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4403,7 +4398,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4446,7 +4441,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4460,10 +4455,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4481,7 +4476,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4524,7 +4519,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4538,10 +4533,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46044</v>
+        <v>46162</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4553,8 +4548,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45628</v>
+        <v>46162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4628,11 +4628,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45588</v>
+        <v>45631</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45181</v>
+        <v>45588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45448</v>
+        <v>45282</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4894,7 +4894,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45631</v>
+        <v>45181</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45211</v>
+        <v>44782</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5040,7 +5040,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46132</v>
+        <v>44727</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5113,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46132</v>
+        <v>46204</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5142,8 +5142,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>9.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5186,7 +5191,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5200,10 +5205,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46132</v>
+        <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5215,8 +5220,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5259,7 +5269,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5273,10 +5283,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5294,7 +5304,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5337,7 +5347,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5354,7 +5364,7 @@
         <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5366,8 +5376,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5410,7 +5425,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5427,7 +5442,7 @@
         <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5440,7 +5455,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5483,7 +5498,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5497,10 +5512,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5512,13 +5527,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5561,7 +5571,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5575,10 +5585,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46205</v>
+        <v>46287</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5606,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5639,7 +5649,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5653,10 +5663,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5668,13 +5678,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5717,7 +5722,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5731,10 +5736,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44727</v>
+        <v>46286</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5747,7 +5752,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5790,7 +5795,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5804,10 +5809,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45282</v>
+        <v>44972</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5820,7 +5825,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5880,7 +5885,7 @@
         <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5936,7 +5941,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5950,10 +5955,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44636</v>
+        <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5966,7 +5971,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6009,7 +6014,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6023,10 +6028,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46286</v>
+        <v>46132</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6039,7 +6044,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6082,7 +6087,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6096,10 +6101,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46244</v>
+        <v>44972</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6112,7 +6117,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6155,7 +6160,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6169,10 +6174,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45699</v>
+        <v>45471</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6184,13 +6189,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6233,7 +6233,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46287</v>
+        <v>45251</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6262,13 +6262,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6328,7 +6323,7 @@
         <v>45387</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6389,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6403,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45251</v>
+        <v>46301</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6419,7 +6414,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6457,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6476,10 +6471,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45251</v>
+        <v>46259</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6491,8 +6486,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6535,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45744</v>
+        <v>45251</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6622,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45188</v>
+        <v>44951</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6681,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45679</v>
+        <v>44957</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46132</v>
+        <v>45234</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45783</v>
+        <v>46272</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46259</v>
+        <v>44967</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7051,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46301</v>
+        <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7124,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45644</v>
+        <v>45699</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,8 +7153,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7197,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7211,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45812</v>
+        <v>44636</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7226,13 +7231,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45827</v>
+        <v>45628</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46272</v>
+        <v>45783</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45251</v>
+        <v>45216</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45644</v>
+        <v>44812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45812</v>
+        <v>45446</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45197</v>
+        <v>44951</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2011,13 +2011,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2060,7 +2055,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,10 +2069,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45903</v>
+        <v>44957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2090,7 +2085,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2133,7 +2128,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2142,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46044</v>
+        <v>45234</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2163,7 +2158,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2206,7 +2201,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45919</v>
+        <v>45644</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2236,7 +2231,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2279,7 +2274,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45926</v>
+        <v>45903</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2308,13 +2303,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2357,7 +2347,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2361,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45095</v>
+        <v>45812</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2386,8 +2376,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2425,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45000</v>
+        <v>45919</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2459,13 +2454,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2525,7 +2515,7 @@
         <v>45827</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2586,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2600,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44790</v>
+        <v>45926</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2615,8 +2605,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2659,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45000</v>
+        <v>45958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2688,13 +2683,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2737,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2751,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2767,7 +2757,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2810,7 +2800,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2824,10 +2814,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45960</v>
+        <v>45000</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2839,8 +2829,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2883,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2897,10 +2892,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44972</v>
+        <v>45968</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2913,7 +2908,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2956,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2970,10 +2965,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45968</v>
+        <v>44782</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2986,7 +2981,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3046,7 +3041,7 @@
         <v>45973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3124,7 +3119,7 @@
         <v>45975</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3180,7 +3175,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46132</v>
+        <v>45980</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3209,8 +3204,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46132</v>
+        <v>46044</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45980</v>
+        <v>45251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3355,13 +3355,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3404,7 +3399,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3418,10 +3413,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46132</v>
+        <v>44972</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3434,7 +3429,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3477,7 +3472,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45216</v>
+        <v>45000</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3506,8 +3501,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45716</v>
+        <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3623,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45827</v>
+        <v>44972</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3652,13 +3652,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3701,7 +3696,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44516</v>
+        <v>45188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3731,7 +3726,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3774,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3788,10 +3783,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45446</v>
+        <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3809,7 +3804,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3852,7 +3847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3866,10 +3861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45188</v>
+        <v>44790</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3882,7 +3877,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3925,7 +3920,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3935,14 +3930,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45211</v>
+        <v>45095</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3955,7 +3950,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3998,7 +3993,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4012,10 +4007,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45272</v>
+        <v>46132</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4028,7 +4023,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4071,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4085,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45448</v>
+        <v>46132</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4101,7 +4096,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4144,7 +4139,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4158,10 +4153,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45679</v>
+        <v>46132</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4174,7 +4169,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4217,7 +4212,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4231,10 +4226,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46153</v>
+        <v>44972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4246,13 +4241,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>8.5</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4295,7 +4285,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4309,10 +4299,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44812</v>
+        <v>44967</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4324,8 +4314,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4368,7 +4363,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4382,10 +4377,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44972</v>
+        <v>45272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4398,7 +4393,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4441,7 +4436,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4455,10 +4450,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46161</v>
+        <v>45471</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4470,13 +4465,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4519,7 +4509,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4533,10 +4523,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46162</v>
+        <v>45716</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4548,13 +4538,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4597,7 +4582,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4611,10 +4596,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46162</v>
+        <v>45827</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4628,11 +4613,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4675,7 +4660,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4689,10 +4674,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45631</v>
+        <v>44516</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4705,7 +4690,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4748,7 +4733,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4762,10 +4747,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45588</v>
+        <v>46153</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4777,8 +4762,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4821,7 +4811,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4835,10 +4825,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45282</v>
+        <v>45628</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4850,8 +4840,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4894,7 +4889,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4908,10 +4903,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45181</v>
+        <v>46161</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4923,8 +4918,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44782</v>
+        <v>46162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4996,8 +4996,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5040,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5054,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44727</v>
+        <v>46162</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5069,8 +5074,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5113,7 +5123,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5127,10 +5137,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46204</v>
+        <v>45181</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5142,13 +5152,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>9.4</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5191,7 +5196,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5205,10 +5210,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46204</v>
+        <v>45448</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5220,13 +5225,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5269,7 +5269,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46205</v>
+        <v>45588</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5298,13 +5298,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5347,7 +5342,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5361,10 +5356,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46205</v>
+        <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5376,13 +5371,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5425,7 +5415,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5435,14 +5425,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46205</v>
+        <v>45211</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5455,7 +5445,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5498,7 +5488,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5512,10 +5502,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5527,8 +5517,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5571,7 +5566,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5585,10 +5580,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46287</v>
+        <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5600,13 +5595,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5649,7 +5639,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5663,10 +5653,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5679,7 +5669,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5722,7 +5712,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5736,10 +5726,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46286</v>
+        <v>46204</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5751,8 +5741,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5795,7 +5790,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5809,10 +5804,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44972</v>
+        <v>46205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5824,8 +5819,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5868,7 +5868,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45420</v>
+        <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5897,8 +5897,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5941,7 +5946,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5955,10 +5960,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45188</v>
+        <v>44727</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5971,7 +5976,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6014,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6028,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46132</v>
+        <v>45282</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6044,7 +6049,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6087,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6101,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44972</v>
+        <v>45420</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6117,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6160,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6174,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45471</v>
+        <v>44636</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6190,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6233,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6247,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45251</v>
+        <v>46286</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6263,7 +6268,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6306,7 +6311,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6316,14 +6321,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45387</v>
+        <v>46244</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6335,13 +6340,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46301</v>
+        <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6413,8 +6413,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6457,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6471,10 +6476,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46259</v>
+        <v>46287</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6535,7 +6540,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6545,14 +6550,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45251</v>
+        <v>45387</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6564,8 +6569,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6608,7 +6618,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6622,10 +6632,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44951</v>
+        <v>45251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6638,7 +6648,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6681,7 +6691,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6695,10 +6705,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45771</v>
+        <v>45251</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6711,7 +6721,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6754,7 +6764,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,10 +6778,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44957</v>
+        <v>45744</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6784,7 +6794,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6827,7 +6837,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6841,10 +6851,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45234</v>
+        <v>45188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6857,7 +6867,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6900,7 +6910,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6914,10 +6924,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46272</v>
+        <v>45251</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6930,7 +6940,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6973,7 +6983,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6987,10 +6997,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44967</v>
+        <v>46132</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7002,13 +7012,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7051,7 +7056,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7065,10 +7070,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45744</v>
+        <v>45679</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7081,7 +7086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7124,7 +7129,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7138,10 +7143,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45699</v>
+        <v>45783</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7153,13 +7158,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44636</v>
+        <v>46259</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7231,8 +7231,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7275,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7289,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45628</v>
+        <v>46301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7304,13 +7309,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45783</v>
+        <v>46272</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45771</v>
+        <v>44727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45216</v>
+        <v>45644</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44812</v>
+        <v>45812</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,8 +1860,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1904,7 +1909,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1918,10 +1923,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45446</v>
+        <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1939,7 +1944,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1982,7 +1987,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1996,10 +2001,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44951</v>
+        <v>44972</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2012,7 +2017,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2055,7 +2060,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2069,10 +2074,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44957</v>
+        <v>45903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2085,7 +2090,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2128,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2142,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45234</v>
+        <v>45420</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2158,7 +2163,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2201,7 +2206,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 45153-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45644</v>
+        <v>45919</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2231,7 +2236,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2274,7 +2279,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 46577-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2288,10 +2293,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45903</v>
+        <v>45926</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2303,8 +2308,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2347,7 +2357,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2361,10 +2371,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45812</v>
+        <v>45188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2376,13 +2386,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2425,7 +2430,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45153-2025</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45919</v>
+        <v>45716</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2455,7 +2460,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2498,7 +2503,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45827</v>
+        <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2527,13 +2532,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2576,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 46577-2025</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45926</v>
+        <v>45471</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2605,13 +2605,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2654,7 +2649,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,10 +2663,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45958</v>
+        <v>45251</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2684,7 +2679,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2727,7 +2722,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2741,10 +2736,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45960</v>
+        <v>45251</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2757,7 +2752,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2800,7 +2795,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2814,10 +2809,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45000</v>
+        <v>45251</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2829,13 +2824,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2878,7 +2868,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2888,14 +2878,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45968</v>
+        <v>45387</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2907,8 +2897,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2951,7 +2946,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44782</v>
+        <v>45827</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2980,8 +2975,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45973</v>
+        <v>45958</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3053,13 +3053,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3102,7 +3097,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 56717-2025</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3116,10 +3111,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45975</v>
+        <v>44516</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3132,7 +3127,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3175,7 +3170,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 57387-2025</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3189,10 +3184,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45980</v>
+        <v>45960</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3204,13 +3199,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3253,7 +3243,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4156-2026</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3267,10 +3257,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46044</v>
+        <v>45968</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3283,7 +3273,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3326,7 +3316,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3340,10 +3330,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45251</v>
+        <v>45973</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3355,8 +3345,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3399,7 +3394,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3413,10 +3408,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44972</v>
+        <v>45251</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3429,7 +3424,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3472,7 +3467,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 56717-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45000</v>
+        <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3501,13 +3496,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3550,7 +3540,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 57387-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3564,10 +3554,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44972</v>
+        <v>45980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3579,8 +3569,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3623,7 +3618,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3637,10 +3632,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44972</v>
+        <v>44951</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3653,7 +3648,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3696,7 +3691,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45188</v>
+        <v>46153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3725,8 +3720,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3769,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45197</v>
+        <v>45771</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3798,13 +3798,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3847,7 +3842,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3861,10 +3856,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44790</v>
+        <v>44957</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3877,7 +3872,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3920,7 +3915,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3934,10 +3929,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45095</v>
+        <v>45234</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3950,7 +3945,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3993,7 +3988,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4007,10 +4002,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4022,8 +4017,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46132</v>
+        <v>46162</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4095,8 +4095,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4139,7 +4144,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4153,10 +4158,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46132</v>
+        <v>44967</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4168,8 +4173,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4212,7 +4222,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4226,10 +4236,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44972</v>
+        <v>46162</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4241,8 +4251,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4285,7 +4300,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4299,10 +4314,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44967</v>
+        <v>45744</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4314,13 +4329,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4363,7 +4373,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4377,10 +4387,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45272</v>
+        <v>45699</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4392,8 +4402,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4436,7 +4451,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4450,10 +4465,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45471</v>
+        <v>45197</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4465,8 +4480,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4509,7 +4529,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4523,10 +4543,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45716</v>
+        <v>44636</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4539,7 +4559,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4582,7 +4602,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4596,10 +4616,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45827</v>
+        <v>45628</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4617,7 +4637,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4660,7 +4680,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 4156-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4674,10 +4694,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44516</v>
+        <v>46044</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4690,7 +4710,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4733,7 +4753,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4747,10 +4767,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46153</v>
+        <v>45588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4762,13 +4782,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4811,7 +4826,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4825,10 +4840,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45628</v>
+        <v>45783</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4840,13 +4855,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4889,7 +4899,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4903,10 +4913,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46161</v>
+        <v>45095</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4918,13 +4928,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4967,7 +4972,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4981,10 +4986,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46162</v>
+        <v>45000</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4998,7 +5003,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -5045,7 +5050,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5059,10 +5064,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46162</v>
+        <v>46204</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5076,11 +5081,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>9.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5123,7 +5128,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5137,10 +5142,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45181</v>
+        <v>46272</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5153,7 +5158,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5196,7 +5201,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5210,10 +5215,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45448</v>
+        <v>46204</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5225,8 +5230,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5269,7 +5279,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5283,10 +5293,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45588</v>
+        <v>46205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5298,8 +5308,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5342,7 +5357,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5356,10 +5371,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45631</v>
+        <v>46205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5371,8 +5386,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5415,7 +5435,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5425,14 +5445,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45211</v>
+        <v>46205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5445,7 +5465,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5488,7 +5508,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5502,10 +5522,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5517,13 +5537,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5566,7 +5581,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5580,10 +5595,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5596,7 +5611,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5639,7 +5654,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5653,10 +5668,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5669,7 +5684,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5712,7 +5727,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5726,10 +5741,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46204</v>
+        <v>46132</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5741,13 +5756,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5790,7 +5800,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5804,10 +5814,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46205</v>
+        <v>44790</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5819,13 +5829,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5868,7 +5873,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5882,10 +5887,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46205</v>
+        <v>45000</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5903,7 +5908,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5946,7 +5951,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5960,10 +5965,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44727</v>
+        <v>44972</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5976,7 +5981,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6019,7 +6024,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6033,10 +6038,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45282</v>
+        <v>46287</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6048,8 +6053,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6092,7 +6102,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6106,10 +6116,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45420</v>
+        <v>46244</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6165,7 +6175,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6179,10 +6189,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44636</v>
+        <v>46286</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6195,7 +6205,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6238,7 +6248,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6252,10 +6262,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46286</v>
+        <v>45216</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6268,7 +6278,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6311,7 +6321,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6325,10 +6335,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46244</v>
+        <v>46132</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6341,7 +6351,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6384,7 +6394,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6398,10 +6408,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45699</v>
+        <v>45446</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6415,11 +6425,11 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6462,7 +6472,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6476,10 +6486,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46287</v>
+        <v>45188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6491,13 +6501,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6540,7 +6545,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6550,14 +6555,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45387</v>
+        <v>45211</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6567,11 +6572,6 @@
       <c r="G80" t="inlineStr">
         <is>
           <t>MUNKFORS</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -6618,7 +6618,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45251</v>
+        <v>45272</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45251</v>
+        <v>45448</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6764,7 +6764,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45744</v>
+        <v>46301</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6837,7 +6837,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45188</v>
+        <v>45679</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45251</v>
+        <v>44812</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46132</v>
+        <v>44972</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45679</v>
+        <v>46259</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7085,8 +7085,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7129,7 +7134,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7143,10 +7148,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45783</v>
+        <v>45631</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7159,7 +7164,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7202,7 +7207,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7216,10 +7221,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46259</v>
+        <v>45282</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7231,13 +7236,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46301</v>
+        <v>45181</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7367,10 +7367,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46272</v>
+        <v>44782</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>17.4</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>54.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>54.4</v>
+        <v>17.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24567-2022</t>
+          <t>A 19994-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44727</v>
+        <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60794-2024</t>
+          <t>A 41967-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45644</v>
+        <v>45903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 27162-2025</t>
+          <t>A 24567-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45812</v>
+        <v>44727</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1860,13 +1860,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1909,7 +1904,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30207-2025</t>
+          <t>A 23012-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1923,10 +1918,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45827</v>
+        <v>46161</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1940,11 +1935,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1987,7 +1982,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 7687-2023</t>
+          <t>A 23212-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2001,10 +1996,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44972</v>
+        <v>46162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2016,8 +2011,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41967-2025</t>
+          <t>A 64772-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45903</v>
+        <v>45282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 18167-2024</t>
+          <t>A 23204-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45420</v>
+        <v>46162</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2162,8 +2162,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2223,7 +2228,7 @@
         <v>45919</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2296,7 +2301,7 @@
         <v>45926</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2357,7 +2362,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44098-2023</t>
+          <t>A 50428-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2371,10 +2376,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45188</v>
+        <v>45216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2387,7 +2392,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2430,7 +2435,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9766-2025</t>
+          <t>A 47625-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2444,10 +2449,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45716</v>
+        <v>45588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2460,7 +2465,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2503,7 +2508,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7646-2023</t>
+          <t>A 18167-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2517,10 +2522,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44972</v>
+        <v>45420</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2533,7 +2538,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2576,7 +2581,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27069-2024</t>
+          <t>A 12114-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2590,10 +2595,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45471</v>
+        <v>44636</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2606,7 +2611,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2649,7 +2654,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59128-2023</t>
+          <t>A 53284-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45251</v>
+        <v>45958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2679,7 +2684,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2722,7 +2727,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59137-2023</t>
+          <t>A 6579-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2736,10 +2741,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45251</v>
+        <v>45699</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2751,8 +2756,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2795,7 +2805,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59132-2023</t>
+          <t>A 53524-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2809,10 +2819,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45251</v>
+        <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2825,7 +2835,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2868,7 +2878,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13431-2024</t>
+          <t>A 55254-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2878,14 +2888,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45387</v>
+        <v>45968</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2897,13 +2907,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2946,7 +2951,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30160-2025</t>
+          <t>A 13431-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2956,14 +2961,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45827</v>
+        <v>45387</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2981,7 +2986,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3024,7 +3029,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53284-2025</t>
+          <t>A 38238-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3038,10 +3043,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45958</v>
+        <v>44812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3054,7 +3059,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.3</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3097,7 +3102,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 65754-2021</t>
+          <t>A 59128-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3111,10 +3116,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44516</v>
+        <v>45251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3127,7 +3132,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3170,7 +3175,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 53524-2025</t>
+          <t>A 59137-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3184,10 +3189,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45960</v>
+        <v>45251</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3200,7 +3205,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3243,7 +3248,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 55254-2025</t>
+          <t>A 56023-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3257,10 +3262,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45968</v>
+        <v>45973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3272,8 +3277,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3316,7 +3326,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 56023-2025</t>
+          <t>A 15125-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3330,10 +3340,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45973</v>
+        <v>45744</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3345,13 +3355,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59146-2023</t>
+          <t>A 44104-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3408,10 +3413,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45251</v>
+        <v>45188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3484,7 +3489,7 @@
         <v>45975</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3557,7 +3562,7 @@
         <v>45980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3618,7 +3623,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4610-2023</t>
+          <t>A 29672-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3632,10 +3637,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44951</v>
+        <v>46204</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3647,8 +3652,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3691,7 +3701,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22096-2026</t>
+          <t>A 29992-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46153</v>
+        <v>46205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3720,13 +3730,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>8.5</v>
+        <v>4.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3769,7 +3774,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19994-2025</t>
+          <t>A 29985-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3783,10 +3788,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45771</v>
+        <v>46205</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3799,7 +3804,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3842,7 +3847,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4795-2023</t>
+          <t>A 29609-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3856,10 +3861,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44957</v>
+        <v>46204</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3871,8 +3876,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3915,7 +3925,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54628-2023</t>
+          <t>A 29908-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3929,10 +3939,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45234</v>
+        <v>46205</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3944,8 +3954,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3988,7 +4003,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 23012-2026</t>
+          <t>A 29951-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4002,10 +4017,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46161</v>
+        <v>46205</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4019,11 +4034,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4066,7 +4081,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23212-2026</t>
+          <t>A 59132-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4080,10 +4095,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46162</v>
+        <v>45251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4095,13 +4110,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4144,7 +4154,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6859-2023</t>
+          <t>A 3333-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4158,10 +4168,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44967</v>
+        <v>45679</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4173,13 +4183,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4222,7 +4227,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23204-2026</t>
+          <t>A 22225-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4236,10 +4241,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46162</v>
+        <v>45446</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4253,11 +4258,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4300,7 +4305,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15125-2025</t>
+          <t>A 21614-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4314,10 +4319,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45744</v>
+        <v>45783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4330,7 +4335,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4373,7 +4378,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6579-2025</t>
+          <t>A 4610-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4387,10 +4392,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45699</v>
+        <v>44951</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4402,13 +4407,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 46447-2023</t>
+          <t>A 38961-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45197</v>
+        <v>46286</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4480,13 +4480,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4529,7 +4524,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12114-2022</t>
+          <t>A 32900-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44636</v>
+        <v>46244</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4559,7 +4554,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4602,7 +4597,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 56776-2024</t>
+          <t>A 39069-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4616,10 +4611,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45628</v>
+        <v>46287</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4697,7 +4692,7 @@
         <v>46044</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4753,7 +4748,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47625-2024</t>
+          <t>A 60794-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4767,10 +4762,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45588</v>
+        <v>45644</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4783,7 +4778,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4826,7 +4821,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 21614-2025</t>
+          <t>A 4795-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4840,10 +4835,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45783</v>
+        <v>44957</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4856,7 +4851,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4899,7 +4894,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 27045-2023</t>
+          <t>A 27162-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4913,10 +4908,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45095</v>
+        <v>45812</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4928,8 +4923,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4972,7 +4972,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12588-2023</t>
+          <t>A 19220-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45000</v>
+        <v>46132</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5001,13 +5001,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5050,7 +5045,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29609-2026</t>
+          <t>A 30207-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5064,10 +5059,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46204</v>
+        <v>45827</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5085,7 +5080,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5128,7 +5123,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36841-2026</t>
+          <t>A 54628-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5142,10 +5137,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46272</v>
+        <v>45234</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5158,7 +5153,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5201,7 +5196,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29672-2026</t>
+          <t>A 34981-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5215,10 +5210,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46204</v>
+        <v>46259</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5236,7 +5231,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5279,7 +5274,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29908-2026</t>
+          <t>A 41579-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5293,10 +5288,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46205</v>
+        <v>46301</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5308,13 +5303,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5357,7 +5347,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29951-2026</t>
+          <t>A 19207-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5371,10 +5361,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5386,13 +5376,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5435,7 +5420,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29992-2026</t>
+          <t>A 19208-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5449,10 +5434,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5465,7 +5450,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5508,7 +5493,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29985-2026</t>
+          <t>A 19172-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5522,10 +5507,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46205</v>
+        <v>46132</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5538,7 +5523,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5581,7 +5566,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19207-2026</t>
+          <t>A 9766-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5595,10 +5580,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46132</v>
+        <v>45716</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5611,7 +5596,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5654,7 +5639,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19208-2026</t>
+          <t>A 30160-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5668,10 +5653,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46132</v>
+        <v>45827</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5683,8 +5668,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5727,7 +5717,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19172-2026</t>
+          <t>A 65754-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5741,10 +5731,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46132</v>
+        <v>44516</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5757,7 +5747,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5800,7 +5790,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 33908-2022</t>
+          <t>A 36841-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5814,10 +5804,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44790</v>
+        <v>46272</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5830,7 +5820,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5873,7 +5863,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12563-2023</t>
+          <t>A 12588-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5890,7 +5880,7 @@
         <v>45000</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5908,7 +5898,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5951,7 +5941,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7683-2023</t>
+          <t>A 22096-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5965,10 +5955,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44972</v>
+        <v>46153</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5980,8 +5970,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.2</v>
+        <v>8.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6024,7 +6019,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39069-2026</t>
+          <t>A 32389-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6038,10 +6033,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46287</v>
+        <v>44782</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6053,13 +6048,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6102,7 +6092,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32900-2026</t>
+          <t>A 59146-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6116,10 +6106,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46244</v>
+        <v>45251</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6132,7 +6122,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6175,7 +6165,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38961-2026</t>
+          <t>A 7688-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6189,10 +6179,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46286</v>
+        <v>44972</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6205,7 +6195,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6248,7 +6238,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50428-2023</t>
+          <t>A 12563-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6262,10 +6252,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45216</v>
+        <v>45000</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6277,8 +6267,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6321,7 +6316,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 19220-2026</t>
+          <t>A 7683-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6335,10 +6330,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46132</v>
+        <v>44972</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6351,7 +6346,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6394,7 +6389,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22225-2024</t>
+          <t>A 7687-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6408,10 +6403,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45446</v>
+        <v>44972</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6423,13 +6418,8 @@
           <t>MUNKFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6472,7 +6462,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44104-2023</t>
+          <t>A 44098-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6489,7 +6479,7 @@
         <v>45188</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6502,7 +6492,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6545,7 +6535,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49500-2023</t>
+          <t>A 46447-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6555,14 +6545,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45211</v>
+        <v>45197</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6574,8 +6564,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6618,7 +6613,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62977-2023</t>
+          <t>A 33908-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6632,10 +6627,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45272</v>
+        <v>44790</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6648,7 +6643,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6691,7 +6686,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 22757-2024</t>
+          <t>A 27045-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6705,10 +6700,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45448</v>
+        <v>45095</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6721,7 +6716,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6764,7 +6759,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41579-2026</t>
+          <t>A 7646-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6778,10 +6773,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46301</v>
+        <v>44972</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6794,7 +6789,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6837,7 +6832,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3333-2025</t>
+          <t>A 6859-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6851,10 +6846,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45679</v>
+        <v>44967</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6866,8 +6861,13 @@
           <t>MUNKFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38238-2022</t>
+          <t>A 62977-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44812</v>
+        <v>45272</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7688-2023</t>
+          <t>A 27069-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44972</v>
+        <v>45471</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7056,7 +7056,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34981-2026</t>
+          <t>A 56776-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46259</v>
+        <v>45628</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58050-2024</t>
+          <t>A 42637-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45631</v>
+        <v>45181</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 64772-2023</t>
+          <t>A 22757-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45282</v>
+        <v>45448</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42637-2023</t>
+          <t>A 58050-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45181</v>
+        <v>45631</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32389-2022</t>
+          <t>A 49500-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7363,14 +7363,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44782</v>
+        <v>45211</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7426,7 +7426,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S 4412-2023</t>
+          <t>S 932-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.5</v>
+        <v>52.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S 4417-2023</t>
+          <t>S 923-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>17.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7582,7 +7582,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>S 932-2022</t>
+          <t>S 4412-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>52.1</v>
+        <v>12.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7660,7 +7660,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S 6971-2022</t>
+          <t>S 4417-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7674,10 +7674,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44901</v>
+        <v>45266</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7738,7 +7738,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S 4413-2023</t>
+          <t>S 6971-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>44901</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>54.4</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>S 923-2022</t>
+          <t>S 4413-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44606</v>
+        <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>17.4</v>
+        <v>54.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7911,7 +7911,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>

--- a/Översikt MUNKFORS.xlsx
+++ b/Översikt MUNKFORS.xlsx
@@ -601,7 +601,7 @@
         <v>44566</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>45188</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46258</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>46009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44747</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>44727</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>44531</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>44648</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>44825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44648</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>44648</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>44685</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45771</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45903</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>44727</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46161</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>46162</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>46162</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45919</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45926</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>45216</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45588</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45420</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>44636</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45699</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45960</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45968</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45387</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44812</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45251</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>45251</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>45973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45744</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319